--- a/data/indicadores/07_01_01_04_mcc.xlsx
+++ b/data/indicadores/07_01_01_04_mcc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\Indicadores_Fabiana\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Final\Input_indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACACDF3-7ECF-4FF9-A28F-86DE7FFEAEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80DE599-48B3-4322-BAF4-458A35F2EB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datos_2016" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId9"/>
-    <pivotCache cacheId="5" r:id="rId10"/>
+    <pivotCache cacheId="19" r:id="rId9"/>
+    <pivotCache cacheId="20" r:id="rId10"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -1395,7 +1395,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1454,8 +1454,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares 2" xfId="3" xr:uid="{503ADE39-8104-4FA7-B6A3-B3E53CE3E60E}"/>
@@ -1998,7 +1996,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Karina" refreshedDate="46178.045990972219" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="325" xr:uid="{90B52A1C-387A-41C9-BC79-8F66AD8900C2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Karina" refreshedDate="46180.105755324075" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="325" xr:uid="{90B52A1C-387A-41C9-BC79-8F66AD8900C2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G326" sheet="datos_2024"/>
   </cacheSource>
@@ -8266,7 +8264,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11B9D805-FC74-440B-916E-120034756E33}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11B9D805-FC74-440B-916E-120034756E33}" name="TablaDinámica3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="K14:M18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -8655,7 +8653,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3DA408D1-4802-4B76-BF26-4B4E2D74DD31}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3DA408D1-4802-4B76-BF26-4B4E2D74DD31}" name="TablaDinámica2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="K1:M11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0">
@@ -8742,7 +8740,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9BC5333-DAAF-4B9D-8425-170039A81DD4}" name="TablaDinámica5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9BC5333-DAAF-4B9D-8425-170039A81DD4}" name="TablaDinámica5" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="K1:M11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0">
@@ -8829,7 +8827,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CBA2883-B431-4964-80F0-E17B13F8749B}" name="TablaDinámica4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CBA2883-B431-4964-80F0-E17B13F8749B}" name="TablaDinámica4" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="K14:M18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -9226,7 +9224,7 @@
       <calculatedColumnFormula>IFERROR(VLOOKUP(A2,datos_2016!$B$1:$G$330,6,FALSE),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7799B7E2-ACD9-4874-954B-382E6BBE9CB3}" name="Porcentaje de medidores eléctricos residenciales con consumo cero 2023 (%)" dataDxfId="0" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(A2,datos_2024!$B$1:$G$322,6,FALSE),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IFERROR(VLOOKUP(A2,datos_2024!$B$1:$G$342,6,FALSE),"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -18060,10 +18058,10 @@
       <c r="K2" s="15">
         <v>1</v>
       </c>
-      <c r="L2" s="32">
+      <c r="L2">
         <v>161477</v>
       </c>
-      <c r="M2" s="32">
+      <c r="M2">
         <v>14070</v>
       </c>
       <c r="N2">
@@ -18098,10 +18096,10 @@
       <c r="K3" s="15">
         <v>2</v>
       </c>
-      <c r="L3" s="32">
+      <c r="L3">
         <v>939628</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3">
         <v>85646</v>
       </c>
       <c r="N3">
@@ -18136,10 +18134,10 @@
       <c r="K4" s="15">
         <v>3</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4">
         <v>644512</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4">
         <v>43576</v>
       </c>
       <c r="N4">
@@ -18174,10 +18172,10 @@
       <c r="K5" s="15">
         <v>4</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5">
         <v>157865</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5">
         <v>15874</v>
       </c>
       <c r="N5">
@@ -18212,10 +18210,10 @@
       <c r="K6" s="15">
         <v>5</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6">
         <v>191598</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6">
         <v>22042</v>
       </c>
       <c r="N6">
@@ -18250,10 +18248,10 @@
       <c r="K7" s="15">
         <v>6</v>
       </c>
-      <c r="L7" s="32">
+      <c r="L7">
         <v>147330</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7">
         <v>10572</v>
       </c>
       <c r="N7">
@@ -18288,10 +18286,10 @@
       <c r="K8" s="15">
         <v>7</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8">
         <v>663439</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8">
         <v>45446</v>
       </c>
       <c r="N8">
@@ -18326,10 +18324,10 @@
       <c r="K9" s="15">
         <v>8</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9">
         <v>99658</v>
       </c>
-      <c r="M9" s="32">
+      <c r="M9">
         <v>1957</v>
       </c>
       <c r="N9">
@@ -18364,10 +18362,10 @@
       <c r="K10" s="15">
         <v>9</v>
       </c>
-      <c r="L10" s="32">
+      <c r="L10">
         <v>21843</v>
       </c>
-      <c r="M10" s="32">
+      <c r="M10">
         <v>471</v>
       </c>
       <c r="N10">
@@ -18402,10 +18400,10 @@
       <c r="K11" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="L11" s="32">
+      <c r="L11">
         <v>3027350</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M11">
         <v>239654</v>
       </c>
       <c r="N11">
@@ -18524,10 +18522,10 @@
       <c r="K15" s="15">
         <v>60301</v>
       </c>
-      <c r="L15" s="32">
+      <c r="L15">
         <v>25327</v>
       </c>
-      <c r="M15" s="32">
+      <c r="M15">
         <v>1144</v>
       </c>
       <c r="N15">
@@ -18562,10 +18560,10 @@
       <c r="K16" s="15">
         <v>60302</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16">
         <v>4392</v>
       </c>
-      <c r="M16" s="32">
+      <c r="M16">
         <v>418</v>
       </c>
       <c r="N16">
@@ -18600,10 +18598,10 @@
       <c r="K17" s="15">
         <v>60303</v>
       </c>
-      <c r="L17" s="32">
+      <c r="L17">
         <v>13201</v>
       </c>
-      <c r="M17" s="32">
+      <c r="M17">
         <v>718</v>
       </c>
       <c r="N17">
@@ -18638,10 +18636,10 @@
       <c r="K18" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="L18" s="32">
+      <c r="L18">
         <v>42920</v>
       </c>
-      <c r="M18" s="32">
+      <c r="M18">
         <v>2280</v>
       </c>
       <c r="N18">
@@ -26389,7 +26387,7 @@
         <v>3.5945917867584858</v>
       </c>
       <c r="D2" s="14">
-        <f>IFERROR(VLOOKUP(A2,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A2,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.2751906949302541</v>
       </c>
     </row>
@@ -26405,7 +26403,7 @@
         <v>11.469387755102041</v>
       </c>
       <c r="D3" s="14">
-        <f>IFERROR(VLOOKUP(A3,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A3,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.721723518850988</v>
       </c>
     </row>
@@ -26421,7 +26419,7 @@
         <v>14.946236559139784</v>
       </c>
       <c r="D4" s="14">
-        <f>IFERROR(VLOOKUP(A4,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A4,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.786764705882353</v>
       </c>
     </row>
@@ -26437,7 +26435,7 @@
         <v>10.771276595744681</v>
       </c>
       <c r="D5" s="14">
-        <f>IFERROR(VLOOKUP(A5,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A5,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.494133885438234</v>
       </c>
     </row>
@@ -26453,7 +26451,7 @@
         <v>12.298136645962733</v>
       </c>
       <c r="D6" s="14">
-        <f>IFERROR(VLOOKUP(A6,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A6,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.458804523424879</v>
       </c>
     </row>
@@ -26469,7 +26467,7 @@
         <v>13.682277318640955</v>
       </c>
       <c r="D7" s="14">
-        <f>IFERROR(VLOOKUP(A7,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A7,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.723459347488348</v>
       </c>
     </row>
@@ -26485,7 +26483,7 @@
         <v>8.120868744098205</v>
       </c>
       <c r="D8" s="14">
-        <f>IFERROR(VLOOKUP(A8,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A8,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.8804347826086953</v>
       </c>
     </row>
@@ -26501,7 +26499,7 @@
         <v>9.453125</v>
       </c>
       <c r="D9" s="14">
-        <f>IFERROR(VLOOKUP(A9,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A9,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.517467248908297</v>
       </c>
     </row>
@@ -26517,7 +26515,7 @@
         <v>10.603715170278639</v>
       </c>
       <c r="D10" s="14">
-        <f>IFERROR(VLOOKUP(A10,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A10,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.427807486631016</v>
       </c>
     </row>
@@ -26533,7 +26531,7 @@
         <v>8.9014084507042259</v>
       </c>
       <c r="D11" s="14">
-        <f>IFERROR(VLOOKUP(A11,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A11,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.861694424330196</v>
       </c>
     </row>
@@ -26549,7 +26547,7 @@
         <v>8.5910652920962196</v>
       </c>
       <c r="D12" s="14">
-        <f>IFERROR(VLOOKUP(A12,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A12,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.475633528265107</v>
       </c>
     </row>
@@ -26565,7 +26563,7 @@
         <v>5.0125313283208017</v>
       </c>
       <c r="D13" s="14">
-        <f>IFERROR(VLOOKUP(A13,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A13,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.740458015267176</v>
       </c>
     </row>
@@ -26581,7 +26579,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="14">
-        <f>IFERROR(VLOOKUP(A14,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A14,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.113122171945701</v>
       </c>
     </row>
@@ -26597,7 +26595,7 @@
         <v>20.346820809248555</v>
       </c>
       <c r="D15" s="14">
-        <f>IFERROR(VLOOKUP(A15,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A15,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.503305004721435</v>
       </c>
     </row>
@@ -26613,7 +26611,7 @@
         <v>4.2787000233808747</v>
       </c>
       <c r="D16" s="14">
-        <f>IFERROR(VLOOKUP(A16,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A16,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.2862374122673179</v>
       </c>
     </row>
@@ -26629,7 +26627,7 @@
         <v>3.1968031968031969</v>
       </c>
       <c r="D17" s="14">
-        <f>IFERROR(VLOOKUP(A17,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A17,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.3277967757694187</v>
       </c>
     </row>
@@ -26645,7 +26643,7 @@
         <v>8.7099424815119146</v>
       </c>
       <c r="D18" s="14">
-        <f>IFERROR(VLOOKUP(A18,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A18,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.743756786102063</v>
       </c>
     </row>
@@ -26661,7 +26659,7 @@
         <v>11.366245694603904</v>
       </c>
       <c r="D19" s="14">
-        <f>IFERROR(VLOOKUP(A19,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A19,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.92242532322782</v>
       </c>
     </row>
@@ -26677,7 +26675,7 @@
         <v>10.78129375525063</v>
       </c>
       <c r="D20" s="14">
-        <f>IFERROR(VLOOKUP(A20,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A20,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.914121292607348</v>
       </c>
     </row>
@@ -26693,7 +26691,7 @@
         <v>17.571466037241017</v>
       </c>
       <c r="D21" s="14">
-        <f>IFERROR(VLOOKUP(A21,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A21,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>23.201438848920862</v>
       </c>
     </row>
@@ -26709,7 +26707,7 @@
         <v>7.6761303890641432</v>
       </c>
       <c r="D22" s="14">
-        <f>IFERROR(VLOOKUP(A22,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A22,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.736842105263158</v>
       </c>
     </row>
@@ -26725,7 +26723,7 @@
         <v>9.4226579520697165</v>
       </c>
       <c r="D23" s="14">
-        <f>IFERROR(VLOOKUP(A23,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A23,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.471698113207546</v>
       </c>
     </row>
@@ -26741,7 +26739,7 @@
         <v>10.931899641577061</v>
       </c>
       <c r="D24" s="14">
-        <f>IFERROR(VLOOKUP(A24,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A24,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.688622754491018</v>
       </c>
     </row>
@@ -26757,7 +26755,7 @@
         <v>11.878787878787879</v>
       </c>
       <c r="D25" s="14">
-        <f>IFERROR(VLOOKUP(A25,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A25,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.685185185185187</v>
       </c>
     </row>
@@ -26773,7 +26771,7 @@
         <v>8.6715079026057236</v>
       </c>
       <c r="D26" s="14">
-        <f>IFERROR(VLOOKUP(A26,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A26,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.214681440443213</v>
       </c>
     </row>
@@ -26789,7 +26787,7 @@
         <v>11.180904522613066</v>
       </c>
       <c r="D27" s="14">
-        <f>IFERROR(VLOOKUP(A27,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A27,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.057171514543629</v>
       </c>
     </row>
@@ -26805,7 +26803,7 @@
         <v>1.6521739130434783</v>
       </c>
       <c r="D28" s="14">
-        <f>IFERROR(VLOOKUP(A28,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A28,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.3563111318118306</v>
       </c>
     </row>
@@ -26821,7 +26819,7 @@
         <v>7.6045627376425857</v>
       </c>
       <c r="D29" s="14">
-        <f>IFERROR(VLOOKUP(A29,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A29,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.428571428571429</v>
       </c>
     </row>
@@ -26837,7 +26835,7 @@
         <v>6.5554231227651965</v>
       </c>
       <c r="D30" s="14">
-        <f>IFERROR(VLOOKUP(A30,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A30,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.349896480331263</v>
       </c>
     </row>
@@ -26853,7 +26851,7 @@
         <v>4.398383615961194</v>
       </c>
       <c r="D31" s="14">
-        <f>IFERROR(VLOOKUP(A31,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A31,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.9893116785158318</v>
       </c>
     </row>
@@ -26869,7 +26867,7 @@
         <v>8.4018022793532996</v>
       </c>
       <c r="D32" s="14">
-        <f>IFERROR(VLOOKUP(A32,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A32,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.3836246550137989</v>
       </c>
     </row>
@@ -26885,7 +26883,7 @@
         <v>10.552423900789178</v>
       </c>
       <c r="D33" s="14">
-        <f>IFERROR(VLOOKUP(A33,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A33,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.827665627963691</v>
       </c>
     </row>
@@ -26901,7 +26899,7 @@
         <v>13.54872329338197</v>
       </c>
       <c r="D34" s="14">
-        <f>IFERROR(VLOOKUP(A34,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A34,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.934163118244349</v>
       </c>
     </row>
@@ -26917,7 +26915,7 @@
         <v>7.7712815804350219</v>
       </c>
       <c r="D35" s="14">
-        <f>IFERROR(VLOOKUP(A35,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A35,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.5545089944739834</v>
       </c>
     </row>
@@ -26933,7 +26931,7 @@
         <v>9.2137260199945956</v>
       </c>
       <c r="D36" s="14">
-        <f>IFERROR(VLOOKUP(A36,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A36,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.583608967291436</v>
       </c>
     </row>
@@ -26949,7 +26947,7 @@
         <v>21.349009900990097</v>
       </c>
       <c r="D37" s="14">
-        <f>IFERROR(VLOOKUP(A37,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A37,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.355983162958509</v>
       </c>
     </row>
@@ -26965,7 +26963,7 @@
         <v>13.340807174887892</v>
       </c>
       <c r="D38" s="14">
-        <f>IFERROR(VLOOKUP(A38,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A38,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.289592760180994</v>
       </c>
     </row>
@@ -26981,7 +26979,7 @@
         <v>18.160831088880339</v>
       </c>
       <c r="D39" s="14">
-        <f>IFERROR(VLOOKUP(A39,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A39,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.159782115297322</v>
       </c>
     </row>
@@ -26997,7 +26995,7 @@
         <v>18.974175035868004</v>
       </c>
       <c r="D40" s="14">
-        <f>IFERROR(VLOOKUP(A40,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A40,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>22.084998183799492</v>
       </c>
     </row>
@@ -27013,7 +27011,7 @@
         <v>20.17067494181536</v>
       </c>
       <c r="D41" s="14">
-        <f>IFERROR(VLOOKUP(A41,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A41,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.864406779661017</v>
       </c>
     </row>
@@ -27029,7 +27027,7 @@
         <v>26.058743169398905</v>
       </c>
       <c r="D42" s="14">
-        <f>IFERROR(VLOOKUP(A42,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A42,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>26.715945089757128</v>
       </c>
     </row>
@@ -27045,7 +27043,7 @@
         <v>27.28358208955224</v>
       </c>
       <c r="D43" s="14">
-        <f>IFERROR(VLOOKUP(A43,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A43,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>30.045662100456621</v>
       </c>
     </row>
@@ -27061,7 +27059,7 @@
         <v>30.680813439434129</v>
       </c>
       <c r="D44" s="14">
-        <f>IFERROR(VLOOKUP(A44,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A44,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>33.674082982561636</v>
       </c>
     </row>
@@ -27077,7 +27075,7 @@
         <v>20.68230277185501</v>
       </c>
       <c r="D45" s="14">
-        <f>IFERROR(VLOOKUP(A45,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A45,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>26.198630136986303</v>
       </c>
     </row>
@@ -27093,7 +27091,7 @@
         <v>17.478510028653297</v>
       </c>
       <c r="D46" s="14">
-        <f>IFERROR(VLOOKUP(A46,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A46,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.331658291457288</v>
       </c>
     </row>
@@ -27109,7 +27107,7 @@
         <v>16.981132075471699</v>
       </c>
       <c r="D47" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A47,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A47,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -27125,7 +27123,7 @@
         <v>16.831683168316832</v>
       </c>
       <c r="D48" s="14">
-        <f>IFERROR(VLOOKUP(A48,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A48,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>23.076923076923077</v>
       </c>
     </row>
@@ -27141,7 +27139,7 @@
         <v>49.63680387409201</v>
       </c>
       <c r="D49" s="14">
-        <f>IFERROR(VLOOKUP(A49,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A49,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>34.834437086092713</v>
       </c>
     </row>
@@ -27157,7 +27155,7 @@
         <v>10.851387305207146</v>
       </c>
       <c r="D50" s="14">
-        <f>IFERROR(VLOOKUP(A50,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A50,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.907335907335908</v>
       </c>
     </row>
@@ -27173,7 +27171,7 @@
         <v>13.030484160191273</v>
       </c>
       <c r="D51" s="14">
-        <f>IFERROR(VLOOKUP(A51,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A51,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.59322033898305</v>
       </c>
     </row>
@@ -27189,7 +27187,7 @@
         <v>15.62944018186985</v>
       </c>
       <c r="D52" s="14">
-        <f>IFERROR(VLOOKUP(A52,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A52,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.857677902621722</v>
       </c>
     </row>
@@ -27205,7 +27203,7 @@
         <v>12.147887323943662</v>
       </c>
       <c r="D53" s="14">
-        <f>IFERROR(VLOOKUP(A53,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A53,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.008779631255488</v>
       </c>
     </row>
@@ -27221,7 +27219,7 @@
         <v>15.473684210526315</v>
       </c>
       <c r="D54" s="14">
-        <f>IFERROR(VLOOKUP(A54,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A54,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.843941537010844</v>
       </c>
     </row>
@@ -27237,7 +27235,7 @@
         <v>18.426770969143849</v>
       </c>
       <c r="D55" s="14">
-        <f>IFERROR(VLOOKUP(A55,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A55,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.601645123384253</v>
       </c>
     </row>
@@ -27253,7 +27251,7 @@
         <v>10.762032085561497</v>
       </c>
       <c r="D56" s="14">
-        <f>IFERROR(VLOOKUP(A56,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A56,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.969058591178406</v>
       </c>
     </row>
@@ -27269,7 +27267,7 @@
         <v>16.726403823178018</v>
       </c>
       <c r="D57" s="14">
-        <f>IFERROR(VLOOKUP(A57,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A57,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.6816720257234721</v>
       </c>
     </row>
@@ -27285,7 +27283,7 @@
         <v>18.863049095607234</v>
       </c>
       <c r="D58" s="14">
-        <f>IFERROR(VLOOKUP(A58,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A58,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.798582398109865</v>
       </c>
     </row>
@@ -27301,7 +27299,7 @@
         <v>7.1890145395799676</v>
       </c>
       <c r="D59" s="14">
-        <f>IFERROR(VLOOKUP(A59,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A59,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.0808729139922977</v>
       </c>
     </row>
@@ -27317,7 +27315,7 @@
         <v>14.206514206514207</v>
       </c>
       <c r="D60" s="14">
-        <f>IFERROR(VLOOKUP(A60,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A60,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.922252010723861</v>
       </c>
     </row>
@@ -27333,7 +27331,7 @@
         <v>15.414012738853502</v>
       </c>
       <c r="D61" s="14">
-        <f>IFERROR(VLOOKUP(A61,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A61,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.3552465233881161</v>
       </c>
     </row>
@@ -27349,7 +27347,7 @@
         <v>23.040752351097179</v>
       </c>
       <c r="D62" s="14">
-        <f>IFERROR(VLOOKUP(A62,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A62,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.235494880546074</v>
       </c>
     </row>
@@ -27365,7 +27363,7 @@
         <v>8.8490770901194349</v>
       </c>
       <c r="D63" s="14">
-        <f>IFERROR(VLOOKUP(A63,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A63,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.9030837004405283</v>
       </c>
     </row>
@@ -27381,7 +27379,7 @@
         <v>4.7864127637673697</v>
       </c>
       <c r="D64" s="14">
-        <f>IFERROR(VLOOKUP(A64,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A64,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.3417366946778708</v>
       </c>
     </row>
@@ -27397,7 +27395,7 @@
         <v>7.2100313479623823</v>
       </c>
       <c r="D65" s="14">
-        <f>IFERROR(VLOOKUP(A65,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A65,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.4539527302363489</v>
       </c>
     </row>
@@ -27413,7 +27411,7 @@
         <v>8.8835119253370198</v>
       </c>
       <c r="D66" s="14">
-        <f>IFERROR(VLOOKUP(A66,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A66,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.5648414985590779</v>
       </c>
     </row>
@@ -27429,7 +27427,7 @@
         <v>14.70281543274244</v>
       </c>
       <c r="D67" s="14">
-        <f>IFERROR(VLOOKUP(A67,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A67,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.006027727546716</v>
       </c>
     </row>
@@ -27445,7 +27443,7 @@
         <v>15.017125101514777</v>
       </c>
       <c r="D68" s="14">
-        <f>IFERROR(VLOOKUP(A68,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A68,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.016340678385738</v>
       </c>
     </row>
@@ -27461,7 +27459,7 @@
         <v>28.9873417721519</v>
       </c>
       <c r="D69" s="14">
-        <f>IFERROR(VLOOKUP(A69,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A69,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.984773505900268</v>
       </c>
     </row>
@@ -27477,7 +27475,7 @@
         <v>17.903930131004365</v>
       </c>
       <c r="D70" s="14">
-        <f>IFERROR(VLOOKUP(A70,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A70,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.556270096463024</v>
       </c>
     </row>
@@ -27493,7 +27491,7 @@
         <v>21.523915461624028</v>
       </c>
       <c r="D71" s="14">
-        <f>IFERROR(VLOOKUP(A71,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A71,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.872986654394845</v>
       </c>
     </row>
@@ -27509,7 +27507,7 @@
         <v>22.805805114029024</v>
       </c>
       <c r="D72" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A72,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A72,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -27525,7 +27523,7 @@
         <v>17.452688495043557</v>
       </c>
       <c r="D73" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A73,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A73,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -27541,7 +27539,7 @@
         <v>21.559322033898304</v>
       </c>
       <c r="D74" s="14">
-        <f>IFERROR(VLOOKUP(A74,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A74,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.143847487001732</v>
       </c>
     </row>
@@ -27557,7 +27555,7 @@
         <v>13.606745879647374</v>
       </c>
       <c r="D75" s="14">
-        <f>IFERROR(VLOOKUP(A75,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A75,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.976478973627939</v>
       </c>
     </row>
@@ -27573,7 +27571,7 @@
         <v>15.496062992125983</v>
       </c>
       <c r="D76" s="14">
-        <f>IFERROR(VLOOKUP(A76,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A76,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.313246162592382</v>
       </c>
     </row>
@@ -27589,7 +27587,7 @@
         <v>22.351421188630489</v>
       </c>
       <c r="D77" s="14">
-        <f>IFERROR(VLOOKUP(A77,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A77,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.455569461827285</v>
       </c>
     </row>
@@ -27605,7 +27603,7 @@
         <v>26.373626373626372</v>
       </c>
       <c r="D78" s="14">
-        <f>IFERROR(VLOOKUP(A78,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A78,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.698412698412698</v>
       </c>
     </row>
@@ -27621,7 +27619,7 @@
         <v>21.340887629839472</v>
       </c>
       <c r="D79" s="14">
-        <f>IFERROR(VLOOKUP(A79,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A79,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.895104895104895</v>
       </c>
     </row>
@@ -27637,7 +27635,7 @@
         <v>12.205270457697642</v>
       </c>
       <c r="D80" s="14">
-        <f>IFERROR(VLOOKUP(A80,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A80,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.360531309297913</v>
       </c>
     </row>
@@ -27653,7 +27651,7 @@
         <v>8.8495575221238933</v>
       </c>
       <c r="D81" s="14">
-        <f>IFERROR(VLOOKUP(A81,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A81,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.3886255924170623</v>
       </c>
     </row>
@@ -27669,7 +27667,7 @@
         <v>8.4259259259259256</v>
       </c>
       <c r="D82" s="14">
-        <f>IFERROR(VLOOKUP(A82,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A82,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.4212465459011359</v>
       </c>
     </row>
@@ -27685,7 +27683,7 @@
         <v>27.13773681515617</v>
       </c>
       <c r="D83" s="14">
-        <f>IFERROR(VLOOKUP(A83,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A83,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.719568567026194</v>
       </c>
     </row>
@@ -27701,7 +27699,7 @@
         <v>34.274586173320351</v>
       </c>
       <c r="D84" s="14">
-        <f>IFERROR(VLOOKUP(A84,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A84,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.370473537604457</v>
       </c>
     </row>
@@ -27717,7 +27715,7 @@
         <v>10.849056603773585</v>
       </c>
       <c r="D85" s="14">
-        <f>IFERROR(VLOOKUP(A85,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A85,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.2278481012658222</v>
       </c>
     </row>
@@ -27733,7 +27731,7 @@
         <v>5.8460180895654092</v>
       </c>
       <c r="D86" s="14">
-        <f>IFERROR(VLOOKUP(A86,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A86,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.7805565339908416</v>
       </c>
     </row>
@@ -27749,7 +27747,7 @@
         <v>7.5908354547558439</v>
       </c>
       <c r="D87" s="14">
-        <f>IFERROR(VLOOKUP(A87,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A87,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.7682563338301041</v>
       </c>
     </row>
@@ -27765,7 +27763,7 @@
         <v>5.4269175108538352</v>
       </c>
       <c r="D88" s="14">
-        <f>IFERROR(VLOOKUP(A88,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A88,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.6652690426275338</v>
       </c>
     </row>
@@ -27781,7 +27779,7 @@
         <v>13.137032842582107</v>
       </c>
       <c r="D89" s="14">
-        <f>IFERROR(VLOOKUP(A89,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A89,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.6159062885326758</v>
       </c>
     </row>
@@ -27797,7 +27795,7 @@
         <v>5.0556117290192111</v>
       </c>
       <c r="D90" s="14">
-        <f>IFERROR(VLOOKUP(A90,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A90,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.3858360766438764</v>
       </c>
     </row>
@@ -27813,7 +27811,7 @@
         <v>17.039586919104991</v>
       </c>
       <c r="D91" s="14">
-        <f>IFERROR(VLOOKUP(A91,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A91,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.368744973248942</v>
       </c>
     </row>
@@ -27829,7 +27827,7 @@
         <v>13.07381052044091</v>
       </c>
       <c r="D92" s="14">
-        <f>IFERROR(VLOOKUP(A92,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A92,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.189817647778728</v>
       </c>
     </row>
@@ -27845,7 +27843,7 @@
         <v>14.589486119314826</v>
       </c>
       <c r="D93" s="14">
-        <f>IFERROR(VLOOKUP(A93,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A93,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.574850299401197</v>
       </c>
     </row>
@@ -27861,7 +27859,7 @@
         <v>13.697164258962012</v>
       </c>
       <c r="D94" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A94,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A94,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -27877,7 +27875,7 @@
         <v>20.648259303721488</v>
       </c>
       <c r="D95" s="14">
-        <f>IFERROR(VLOOKUP(A95,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A95,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.41504937010555</v>
       </c>
     </row>
@@ -27893,7 +27891,7 @@
         <v>29.422718808193668</v>
       </c>
       <c r="D96" s="14">
-        <f>IFERROR(VLOOKUP(A96,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A96,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>28.11606048222313</v>
       </c>
     </row>
@@ -27909,7 +27907,7 @@
         <v>24.261943102522814</v>
       </c>
       <c r="D97" s="14">
-        <f>IFERROR(VLOOKUP(A97,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A97,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.240136385776911</v>
       </c>
     </row>
@@ -27925,7 +27923,7 @@
         <v>16.701977401129945</v>
       </c>
       <c r="D98" s="14">
-        <f>IFERROR(VLOOKUP(A98,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A98,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.045352922389014</v>
       </c>
     </row>
@@ -27941,7 +27939,7 @@
         <v>12.611822487282932</v>
       </c>
       <c r="D99" s="14">
-        <f>IFERROR(VLOOKUP(A99,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A99,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.498541869184836</v>
       </c>
     </row>
@@ -27957,7 +27955,7 @@
         <v>11.452513966480447</v>
       </c>
       <c r="D100" s="14">
-        <f>IFERROR(VLOOKUP(A100,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A100,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.098972922502334</v>
       </c>
     </row>
@@ -27973,7 +27971,7 @@
         <v>6.7415730337078648</v>
       </c>
       <c r="D101" s="14">
-        <f>IFERROR(VLOOKUP(A101,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A101,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.719512195121951</v>
       </c>
     </row>
@@ -27989,7 +27987,7 @@
         <v>4.9785758008569676</v>
       </c>
       <c r="D102" s="14">
-        <f>IFERROR(VLOOKUP(A102,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A102,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.0180859080633002</v>
       </c>
     </row>
@@ -28005,7 +28003,7 @@
         <v>6.4756233717901006</v>
       </c>
       <c r="D103" s="14">
-        <f>IFERROR(VLOOKUP(A103,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A103,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.8389353021177381</v>
       </c>
     </row>
@@ -28021,7 +28019,7 @@
         <v>1.6786570743405276</v>
       </c>
       <c r="D104" s="14">
-        <f>IFERROR(VLOOKUP(A104,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A104,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.6576949620427883</v>
       </c>
     </row>
@@ -28037,7 +28035,7 @@
         <v>2.7491408934707904</v>
       </c>
       <c r="D105" s="14">
-        <f>IFERROR(VLOOKUP(A105,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A105,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>2.3320895522388061</v>
       </c>
     </row>
@@ -28053,7 +28051,7 @@
         <v>13.03205465055176</v>
       </c>
       <c r="D106" s="14">
-        <f>IFERROR(VLOOKUP(A106,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A106,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.049180327868852</v>
       </c>
     </row>
@@ -28069,7 +28067,7 @@
         <v>25</v>
       </c>
       <c r="D107" s="14">
-        <f>IFERROR(VLOOKUP(A107,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A107,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.681159420289855</v>
       </c>
     </row>
@@ -28085,7 +28083,7 @@
         <v>17.704644865652988</v>
       </c>
       <c r="D108" s="14">
-        <f>IFERROR(VLOOKUP(A108,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A108,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.610026789131267</v>
       </c>
     </row>
@@ -28101,7 +28099,7 @@
         <v>18.575498575498575</v>
       </c>
       <c r="D109" s="14">
-        <f>IFERROR(VLOOKUP(A109,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A109,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.175979447655749</v>
       </c>
     </row>
@@ -28117,7 +28115,7 @@
         <v>20.386266094420602</v>
       </c>
       <c r="D110" s="14">
-        <f>IFERROR(VLOOKUP(A110,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A110,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.315175097276263</v>
       </c>
     </row>
@@ -28133,7 +28131,7 @@
         <v>41.666666666666664</v>
       </c>
       <c r="D111" s="14">
-        <f>IFERROR(VLOOKUP(A111,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A111,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.585609593604264</v>
       </c>
     </row>
@@ -28149,7 +28147,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="14">
-        <f>IFERROR(VLOOKUP(A112,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A112,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.593447505584511</v>
       </c>
     </row>
@@ -28165,7 +28163,7 @@
         <v>30.666666666666668</v>
       </c>
       <c r="D113" s="14">
-        <f>IFERROR(VLOOKUP(A113,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A113,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>22.935779816513762</v>
       </c>
     </row>
@@ -28181,7 +28179,7 @@
         <v>21.462264150943398</v>
       </c>
       <c r="D114" s="14">
-        <f>IFERROR(VLOOKUP(A114,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A114,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>22.772861356932154</v>
       </c>
     </row>
@@ -28197,7 +28195,7 @@
         <v>14.871794871794872</v>
       </c>
       <c r="D115" s="14">
-        <f>IFERROR(VLOOKUP(A115,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A115,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.492957746478874</v>
       </c>
     </row>
@@ -28213,7 +28211,7 @@
         <v>14.898944732605974</v>
       </c>
       <c r="D116" s="14">
-        <f>IFERROR(VLOOKUP(A116,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A116,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.913705935314081</v>
       </c>
     </row>
@@ -28229,7 +28227,7 @@
         <v>8.0291970802919703</v>
       </c>
       <c r="D117" s="14">
-        <f>IFERROR(VLOOKUP(A117,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A117,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.483870967741936</v>
       </c>
     </row>
@@ -28245,7 +28243,7 @@
         <v>4.6629897225871266</v>
       </c>
       <c r="D118" s="14">
-        <f>IFERROR(VLOOKUP(A118,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A118,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.6311734416722139</v>
       </c>
     </row>
@@ -28261,7 +28259,7 @@
         <v>6.5300285986653952</v>
       </c>
       <c r="D119" s="14">
-        <f>IFERROR(VLOOKUP(A119,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A119,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.1010534529847833</v>
       </c>
     </row>
@@ -28277,7 +28275,7 @@
         <v>6.1983471074380168</v>
       </c>
       <c r="D120" s="14">
-        <f>IFERROR(VLOOKUP(A120,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A120,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.326860841423947</v>
       </c>
     </row>
@@ -28293,7 +28291,7 @@
         <v>3.5884133160397753</v>
       </c>
       <c r="D121" s="14">
-        <f>IFERROR(VLOOKUP(A121,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A121,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.5177733065057009</v>
       </c>
     </row>
@@ -28309,7 +28307,7 @@
         <v>8.9652956298200515</v>
       </c>
       <c r="D122" s="14">
-        <f>IFERROR(VLOOKUP(A122,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A122,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.964054822860099</v>
       </c>
     </row>
@@ -28325,7 +28323,7 @@
         <v>14.786488209050351</v>
       </c>
       <c r="D123" s="14">
-        <f>IFERROR(VLOOKUP(A123,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A123,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.298076923076923</v>
       </c>
     </row>
@@ -28341,7 +28339,7 @@
         <v>13.898916967509026</v>
       </c>
       <c r="D124" s="14">
-        <f>IFERROR(VLOOKUP(A124,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A124,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.560068405301411</v>
       </c>
     </row>
@@ -28357,7 +28355,7 @@
         <v>11.636079656384226</v>
       </c>
       <c r="D125" s="14">
-        <f>IFERROR(VLOOKUP(A125,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A125,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.427625041404438</v>
       </c>
     </row>
@@ -28373,7 +28371,7 @@
         <v>20</v>
       </c>
       <c r="D126" s="14">
-        <f>IFERROR(VLOOKUP(A126,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A126,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>20.804953560371516</v>
       </c>
     </row>
@@ -28389,7 +28387,7 @@
         <v>16.150442477876105</v>
       </c>
       <c r="D127" s="14">
-        <f>IFERROR(VLOOKUP(A127,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A127,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.007223772779511</v>
       </c>
     </row>
@@ -28405,7 +28403,7 @@
         <v>15.042735042735043</v>
       </c>
       <c r="D128" s="14">
-        <f>IFERROR(VLOOKUP(A128,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A128,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.929016189290163</v>
       </c>
     </row>
@@ -28421,7 +28419,7 @@
         <v>14.810153136144326</v>
       </c>
       <c r="D129" s="14">
-        <f>IFERROR(VLOOKUP(A129,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A129,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.700803212851406</v>
       </c>
     </row>
@@ -28437,7 +28435,7 @@
         <v>16.7531504818384</v>
       </c>
       <c r="D130" s="14">
-        <f>IFERROR(VLOOKUP(A130,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A130,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.30879038317055</v>
       </c>
     </row>
@@ -28453,7 +28451,7 @@
         <v>14.678899082568808</v>
       </c>
       <c r="D131" s="14">
-        <f>IFERROR(VLOOKUP(A131,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A131,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.507977026164646</v>
       </c>
     </row>
@@ -28469,7 +28467,7 @@
         <v>17.863554757630162</v>
       </c>
       <c r="D132" s="14">
-        <f>IFERROR(VLOOKUP(A132,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A132,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.799498746867169</v>
       </c>
     </row>
@@ -28485,7 +28483,7 @@
         <v>5.1048470264695771</v>
       </c>
       <c r="D133" s="14">
-        <f>IFERROR(VLOOKUP(A133,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A133,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.3206494165398279</v>
       </c>
     </row>
@@ -28501,7 +28499,7 @@
         <v>15.838099428068631</v>
       </c>
       <c r="D134" s="14">
-        <f>IFERROR(VLOOKUP(A134,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A134,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.040183696900115</v>
       </c>
     </row>
@@ -28517,7 +28515,7 @@
         <v>5.272407732864675</v>
       </c>
       <c r="D135" s="14">
-        <f>IFERROR(VLOOKUP(A135,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A135,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.1697645600991322</v>
       </c>
     </row>
@@ -28533,7 +28531,7 @@
         <v>10.75768942235559</v>
       </c>
       <c r="D136" s="14">
-        <f>IFERROR(VLOOKUP(A136,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A136,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.155484558040468</v>
       </c>
     </row>
@@ -28549,7 +28547,7 @@
         <v>12.210648148148149</v>
       </c>
       <c r="D137" s="14">
-        <f>IFERROR(VLOOKUP(A137,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A137,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.61119832548404</v>
       </c>
     </row>
@@ -28565,7 +28563,7 @@
         <v>12.396694214876034</v>
       </c>
       <c r="D138" s="14">
-        <f>IFERROR(VLOOKUP(A138,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A138,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.606745879647374</v>
       </c>
     </row>
@@ -28581,7 +28579,7 @@
         <v>3.8903240657850988</v>
       </c>
       <c r="D139" s="14">
-        <f>IFERROR(VLOOKUP(A139,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A139,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.0413130861991959</v>
       </c>
     </row>
@@ -28597,7 +28595,7 @@
         <v>4.3766578249336874</v>
       </c>
       <c r="D140" s="14">
-        <f>IFERROR(VLOOKUP(A140,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A140,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.8090622877955429</v>
       </c>
     </row>
@@ -28613,7 +28611,7 @@
         <v>3.9678943620946341</v>
       </c>
       <c r="D141" s="14">
-        <f>IFERROR(VLOOKUP(A141,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A141,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.747261195464155</v>
       </c>
     </row>
@@ -28629,7 +28627,7 @@
         <v>5.9215955983493807</v>
       </c>
       <c r="D142" s="14">
-        <f>IFERROR(VLOOKUP(A142,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A142,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.3798795882695671</v>
       </c>
     </row>
@@ -28645,7 +28643,7 @@
         <v>3.0338541666666665</v>
       </c>
       <c r="D143" s="14">
-        <f>IFERROR(VLOOKUP(A143,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A143,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.7064663146969901</v>
       </c>
     </row>
@@ -28661,7 +28659,7 @@
         <v>5.7222177838140134</v>
       </c>
       <c r="D144" s="14">
-        <f>IFERROR(VLOOKUP(A144,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A144,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.1093549700634924</v>
       </c>
     </row>
@@ -28677,7 +28675,7 @@
         <v>8.8405238828967647</v>
       </c>
       <c r="D145" s="14">
-        <f>IFERROR(VLOOKUP(A145,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A145,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.9172979797979792</v>
       </c>
     </row>
@@ -28693,7 +28691,7 @@
         <v>7.0631755389861857</v>
       </c>
       <c r="D146" s="14">
-        <f>IFERROR(VLOOKUP(A146,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A146,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.4761319329797322</v>
       </c>
     </row>
@@ -28709,7 +28707,7 @@
         <v>15.81532416502947</v>
       </c>
       <c r="D147" s="14">
-        <f>IFERROR(VLOOKUP(A147,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A147,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.584801762114537</v>
       </c>
     </row>
@@ -28725,7 +28723,7 @@
         <v>6.3647128478389581</v>
       </c>
       <c r="D148" s="14">
-        <f>IFERROR(VLOOKUP(A148,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A148,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.0896605338170513</v>
       </c>
     </row>
@@ -28741,7 +28739,7 @@
         <v>9.7697922515440769</v>
       </c>
       <c r="D149" s="14">
-        <f>IFERROR(VLOOKUP(A149,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A149,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.5912240184757511</v>
       </c>
     </row>
@@ -28757,7 +28755,7 @@
         <v>10.921366163621922</v>
       </c>
       <c r="D150" s="14">
-        <f>IFERROR(VLOOKUP(A150,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A150,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.107089884307328</v>
       </c>
     </row>
@@ -28773,7 +28771,7 @@
         <v>5.6026462683481499</v>
       </c>
       <c r="D151" s="14">
-        <f>IFERROR(VLOOKUP(A151,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A151,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.3036178765665642</v>
       </c>
     </row>
@@ -28789,7 +28787,7 @@
         <v>6.3453598994794476</v>
       </c>
       <c r="D152" s="14">
-        <f>IFERROR(VLOOKUP(A152,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A152,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.7283042011652867</v>
       </c>
     </row>
@@ -28805,7 +28803,7 @@
         <v>3.9094056549336411</v>
       </c>
       <c r="D153" s="14">
-        <f>IFERROR(VLOOKUP(A153,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A153,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.7066620760888274</v>
       </c>
     </row>
@@ -28821,7 +28819,7 @@
         <v>6.8758473755568472</v>
       </c>
       <c r="D154" s="14">
-        <f>IFERROR(VLOOKUP(A154,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A154,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.2326435892477274</v>
       </c>
     </row>
@@ -28837,7 +28835,7 @@
         <v>10.782241014799155</v>
       </c>
       <c r="D155" s="14">
-        <f>IFERROR(VLOOKUP(A155,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A155,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.508538899430739</v>
       </c>
     </row>
@@ -28853,7 +28851,7 @@
         <v>12.794612794612794</v>
       </c>
       <c r="D156" s="14">
-        <f>IFERROR(VLOOKUP(A156,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A156,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.53846153846154</v>
       </c>
     </row>
@@ -28869,7 +28867,7 @@
         <v/>
       </c>
       <c r="D157" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A157,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A157,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -28885,7 +28883,7 @@
         <v>7.8358208955223878</v>
       </c>
       <c r="D158" s="14">
-        <f>IFERROR(VLOOKUP(A158,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A158,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.045397225725095</v>
       </c>
     </row>
@@ -28901,7 +28899,7 @@
         <v>19.314137819475899</v>
       </c>
       <c r="D159" s="14">
-        <f>IFERROR(VLOOKUP(A159,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A159,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.026658203744844</v>
       </c>
     </row>
@@ -28917,7 +28915,7 @@
         <v>10.73224043715847</v>
       </c>
       <c r="D160" s="14">
-        <f>IFERROR(VLOOKUP(A160,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A160,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.593662628145387</v>
       </c>
     </row>
@@ -28933,7 +28931,7 @@
         <v>19.453924914675767</v>
       </c>
       <c r="D161" s="14">
-        <f>IFERROR(VLOOKUP(A161,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A161,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.666666666666668</v>
       </c>
     </row>
@@ -28949,7 +28947,7 @@
         <v/>
       </c>
       <c r="D162" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A162,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A162,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -28965,7 +28963,7 @@
         <v>17.094972067039105</v>
       </c>
       <c r="D163" s="14">
-        <f>IFERROR(VLOOKUP(A163,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A163,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.204801200300075</v>
       </c>
     </row>
@@ -28981,7 +28979,7 @@
         <v>10.51862673484295</v>
       </c>
       <c r="D164" s="14">
-        <f>IFERROR(VLOOKUP(A164,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A164,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.165197857266287</v>
       </c>
     </row>
@@ -28997,7 +28995,7 @@
         <v>4.536082474226804</v>
       </c>
       <c r="D165" s="14">
-        <f>IFERROR(VLOOKUP(A165,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A165,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.7354562155541946</v>
       </c>
     </row>
@@ -29013,7 +29011,7 @@
         <v>5.3643631685351956</v>
       </c>
       <c r="D166" s="14">
-        <f>IFERROR(VLOOKUP(A166,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A166,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.4845558962156229</v>
       </c>
     </row>
@@ -29029,7 +29027,7 @@
         <v>5.2192982456140351</v>
       </c>
       <c r="D167" s="14">
-        <f>IFERROR(VLOOKUP(A167,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A167,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.764337851929092</v>
       </c>
     </row>
@@ -29045,7 +29043,7 @@
         <v>27.710843373493976</v>
       </c>
       <c r="D168" s="14">
-        <f>IFERROR(VLOOKUP(A168,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A168,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.9792663476874</v>
       </c>
     </row>
@@ -29061,7 +29059,7 @@
         <v>1.4160919540229886</v>
       </c>
       <c r="D169" s="14">
-        <f>IFERROR(VLOOKUP(A169,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A169,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.566625155666252</v>
       </c>
     </row>
@@ -29077,7 +29075,7 @@
         <v>16.091008771929825</v>
       </c>
       <c r="D170" s="14">
-        <f>IFERROR(VLOOKUP(A170,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A170,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.14007821117016</v>
       </c>
     </row>
@@ -29093,7 +29091,7 @@
         <v>1.7518248175182483</v>
       </c>
       <c r="D171" s="14">
-        <f>IFERROR(VLOOKUP(A171,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A171,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.384615384615385</v>
       </c>
     </row>
@@ -29109,7 +29107,7 @@
         <v>23.653566229985444</v>
       </c>
       <c r="D172" s="14">
-        <f>IFERROR(VLOOKUP(A172,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A172,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>31.352992194275803</v>
       </c>
     </row>
@@ -29125,7 +29123,7 @@
         <v>29.515418502202643</v>
       </c>
       <c r="D173" s="14">
-        <f>IFERROR(VLOOKUP(A173,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A173,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>24.84375</v>
       </c>
     </row>
@@ -29141,7 +29139,7 @@
         <v>8.7056128293241688</v>
       </c>
       <c r="D174" s="14">
-        <f>IFERROR(VLOOKUP(A174,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A174,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.772823779193207</v>
       </c>
     </row>
@@ -29157,7 +29155,7 @@
         <v>29.18552036199095</v>
       </c>
       <c r="D175" s="14">
-        <f>IFERROR(VLOOKUP(A175,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A175,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>23.486238532110093</v>
       </c>
     </row>
@@ -29173,7 +29171,7 @@
         <v>22.103386809269161</v>
       </c>
       <c r="D176" s="14">
-        <f>IFERROR(VLOOKUP(A176,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A176,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.686746987951807</v>
       </c>
     </row>
@@ -29189,7 +29187,7 @@
         <v>50</v>
       </c>
       <c r="D177" s="14">
-        <f>IFERROR(VLOOKUP(A177,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A177,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>29.098360655737704</v>
       </c>
     </row>
@@ -29205,7 +29203,7 @@
         <v>25.396825396825395</v>
       </c>
       <c r="D178" s="14">
-        <f>IFERROR(VLOOKUP(A178,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A178,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>68.965517241379317</v>
       </c>
     </row>
@@ -29221,7 +29219,7 @@
         <v>1.7241379310344827</v>
       </c>
       <c r="D179" s="14">
-        <f>IFERROR(VLOOKUP(A179,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A179,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>20.3125</v>
       </c>
     </row>
@@ -29237,7 +29235,7 @@
         <v>40.983606557377051</v>
       </c>
       <c r="D180" s="14">
-        <f>IFERROR(VLOOKUP(A180,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A180,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>24.365482233502537</v>
       </c>
     </row>
@@ -29253,7 +29251,7 @@
         <v>26.315789473684209</v>
       </c>
       <c r="D181" s="14">
-        <f>IFERROR(VLOOKUP(A181,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A181,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>30.834512022630836</v>
       </c>
     </row>
@@ -29269,7 +29267,7 @@
         <v>5.7021276595744679</v>
       </c>
       <c r="D182" s="14">
-        <f>IFERROR(VLOOKUP(A182,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A182,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -29285,7 +29283,7 @@
         <v>16.666666666666668</v>
       </c>
       <c r="D183" s="14">
-        <f>IFERROR(VLOOKUP(A183,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A183,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>31.071428571428573</v>
       </c>
     </row>
@@ -29301,7 +29299,7 @@
         <v>8.8067659496230917</v>
       </c>
       <c r="D184" s="14">
-        <f>IFERROR(VLOOKUP(A184,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A184,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.9406068431245966</v>
       </c>
     </row>
@@ -29317,7 +29315,7 @@
         <v>9.6373056994818658</v>
       </c>
       <c r="D185" s="14">
-        <f>IFERROR(VLOOKUP(A185,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A185,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.068965517241379</v>
       </c>
     </row>
@@ -29333,7 +29331,7 @@
         <v>34.702926396689328</v>
       </c>
       <c r="D186" s="14">
-        <f>IFERROR(VLOOKUP(A186,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A186,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.435249526216044</v>
       </c>
     </row>
@@ -29349,7 +29347,7 @@
         <v>33.519553072625698</v>
       </c>
       <c r="D187" s="14">
-        <f>IFERROR(VLOOKUP(A187,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A187,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>20.680628272251308</v>
       </c>
     </row>
@@ -29365,7 +29363,7 @@
         <v>22.965879265091864</v>
       </c>
       <c r="D188" s="14">
-        <f>IFERROR(VLOOKUP(A188,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A188,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.655336505778383</v>
       </c>
     </row>
@@ -29381,7 +29379,7 @@
         <v>14.393939393939394</v>
       </c>
       <c r="D189" s="14">
-        <f>IFERROR(VLOOKUP(A189,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A189,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.49685534591195</v>
       </c>
     </row>
@@ -29397,7 +29395,7 @@
         <v>17.994100294985252</v>
       </c>
       <c r="D190" s="14">
-        <f>IFERROR(VLOOKUP(A190,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A190,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.420289855072465</v>
       </c>
     </row>
@@ -29413,7 +29411,7 @@
         <v>9.9621689785624206</v>
       </c>
       <c r="D191" s="14">
-        <f>IFERROR(VLOOKUP(A191,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A191,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>28.085106382978722</v>
       </c>
     </row>
@@ -29429,7 +29427,7 @@
         <v>0</v>
       </c>
       <c r="D192" s="14">
-        <f>IFERROR(VLOOKUP(A192,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A192,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.3816631130063968</v>
       </c>
     </row>
@@ -29445,7 +29443,7 @@
         <v>25.355871886120998</v>
       </c>
       <c r="D193" s="14">
-        <f>IFERROR(VLOOKUP(A193,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A193,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>31.593038821954483</v>
       </c>
     </row>
@@ -29461,7 +29459,7 @@
         <v>32.054794520547944</v>
       </c>
       <c r="D194" s="14">
-        <f>IFERROR(VLOOKUP(A194,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A194,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -29477,7 +29475,7 @@
         <v>2.1153846153846154</v>
       </c>
       <c r="D195" s="14">
-        <f>IFERROR(VLOOKUP(A195,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A195,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>16.439909297052154</v>
       </c>
     </row>
@@ -29493,7 +29491,7 @@
         <v>15.485362095531586</v>
       </c>
       <c r="D196" s="14">
-        <f>IFERROR(VLOOKUP(A196,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A196,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.847675568743819</v>
       </c>
     </row>
@@ -29509,7 +29507,7 @@
         <v>0</v>
       </c>
       <c r="D197" s="14">
-        <f>IFERROR(VLOOKUP(A197,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A197,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.463087248322147</v>
       </c>
     </row>
@@ -29525,7 +29523,7 @@
         <v>0</v>
       </c>
       <c r="D198" s="14">
-        <f>IFERROR(VLOOKUP(A198,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A198,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>24.444444444444443</v>
       </c>
     </row>
@@ -29541,7 +29539,7 @@
         <v>0</v>
       </c>
       <c r="D199" s="14">
-        <f>IFERROR(VLOOKUP(A199,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A199,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.458128078817733</v>
       </c>
     </row>
@@ -29557,7 +29555,7 @@
         <v>3.8797284190106693</v>
       </c>
       <c r="D200" s="14">
-        <f>IFERROR(VLOOKUP(A200,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A200,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>23.568575233022635</v>
       </c>
     </row>
@@ -29573,7 +29571,7 @@
         <v>3.907373669575223</v>
       </c>
       <c r="D201" s="14">
-        <f>IFERROR(VLOOKUP(A201,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A201,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.4463246959280802</v>
       </c>
     </row>
@@ -29589,7 +29587,7 @@
         <v>21.969920377469773</v>
       </c>
       <c r="D202" s="14">
-        <f>IFERROR(VLOOKUP(A202,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A202,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>36.035267349260522</v>
       </c>
     </row>
@@ -29605,7 +29603,7 @@
         <v>21.201890614449695</v>
       </c>
       <c r="D203" s="14">
-        <f>IFERROR(VLOOKUP(A203,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A203,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>33.898305084745765</v>
       </c>
     </row>
@@ -29621,7 +29619,7 @@
         <v>34.265734265734267</v>
       </c>
       <c r="D204" s="14">
-        <f>IFERROR(VLOOKUP(A204,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A204,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>39.263803680981596</v>
       </c>
     </row>
@@ -29637,7 +29635,7 @@
         <v>0</v>
       </c>
       <c r="D205" s="14">
-        <f>IFERROR(VLOOKUP(A205,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A205,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -29653,7 +29651,7 @@
         <v>26.437699680511184</v>
       </c>
       <c r="D206" s="14">
-        <f>IFERROR(VLOOKUP(A206,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A206,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>28.177150192554556</v>
       </c>
     </row>
@@ -29669,7 +29667,7 @@
         <v>3.4633145202668034</v>
       </c>
       <c r="D207" s="14">
-        <f>IFERROR(VLOOKUP(A207,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A207,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.6148222608059948</v>
       </c>
     </row>
@@ -29685,7 +29683,7 @@
         <v/>
       </c>
       <c r="D208" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A208,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A208,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -29701,7 +29699,7 @@
         <v>13.540332906530089</v>
       </c>
       <c r="D209" s="14">
-        <f>IFERROR(VLOOKUP(A209,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A209,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.030743664312421</v>
       </c>
     </row>
@@ -29717,7 +29715,7 @@
         <v>11.842105263157896</v>
       </c>
       <c r="D210" s="14">
-        <f>IFERROR(VLOOKUP(A210,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A210,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>27.549271636675236</v>
       </c>
     </row>
@@ -29733,7 +29731,7 @@
         <v>2.7027027027027026</v>
       </c>
       <c r="D211" s="14">
-        <f>IFERROR(VLOOKUP(A211,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A211,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.200948429164197</v>
       </c>
     </row>
@@ -29749,7 +29747,7 @@
         <v>10.646312450436161</v>
       </c>
       <c r="D212" s="14">
-        <f>IFERROR(VLOOKUP(A212,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A212,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>19.710031347962381</v>
       </c>
     </row>
@@ -29765,7 +29763,7 @@
         <v>12.124282337048294</v>
       </c>
       <c r="D213" s="14">
-        <f>IFERROR(VLOOKUP(A213,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A213,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.0271424214699607</v>
       </c>
     </row>
@@ -29781,7 +29779,7 @@
         <v>18.377367313537526</v>
       </c>
       <c r="D214" s="14">
-        <f>IFERROR(VLOOKUP(A214,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A214,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.002763521515988</v>
       </c>
     </row>
@@ -29797,7 +29795,7 @@
         <v>18.546365914786968</v>
       </c>
       <c r="D215" s="14">
-        <f>IFERROR(VLOOKUP(A215,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A215,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.7866108786610884</v>
       </c>
     </row>
@@ -29813,7 +29811,7 @@
         <v/>
       </c>
       <c r="D216" s="14">
-        <f>IFERROR(VLOOKUP(A216,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A216,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>24.766355140186917</v>
       </c>
     </row>
@@ -29829,7 +29827,7 @@
         <v>19.440914866581956</v>
       </c>
       <c r="D217" s="14">
-        <f>IFERROR(VLOOKUP(A217,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A217,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.221337975627954</v>
       </c>
     </row>
@@ -29845,7 +29843,7 @@
         <v>30.515759312320917</v>
       </c>
       <c r="D218" s="14">
-        <f>IFERROR(VLOOKUP(A218,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A218,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.411712511091395</v>
       </c>
     </row>
@@ -29861,7 +29859,7 @@
         <v>18.919427710843372</v>
       </c>
       <c r="D219" s="14">
-        <f>IFERROR(VLOOKUP(A219,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A219,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.185967302452315</v>
       </c>
     </row>
@@ -29877,7 +29875,7 @@
         <v>20.123293703214443</v>
       </c>
       <c r="D220" s="14">
-        <f>IFERROR(VLOOKUP(A220,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A220,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.2405484004985459</v>
       </c>
     </row>
@@ -29893,7 +29891,7 @@
         <v>15.977175463623395</v>
       </c>
       <c r="D221" s="14">
-        <f>IFERROR(VLOOKUP(A221,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A221,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.756446991404012</v>
       </c>
     </row>
@@ -29909,7 +29907,7 @@
         <v>10.323089046493301</v>
       </c>
       <c r="D222" s="14">
-        <f>IFERROR(VLOOKUP(A222,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A222,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>21.17726657645467</v>
       </c>
     </row>
@@ -29925,7 +29923,7 @@
         <v>11.808268229166666</v>
       </c>
       <c r="D223" s="14">
-        <f>IFERROR(VLOOKUP(A223,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A223,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.9784976658650448</v>
       </c>
     </row>
@@ -29941,7 +29939,7 @@
         <v>4.9885132917623896</v>
       </c>
       <c r="D224" s="14">
-        <f>IFERROR(VLOOKUP(A224,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A224,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.635539133355727</v>
       </c>
     </row>
@@ -29957,7 +29955,7 @@
         <v>21.900826446280991</v>
       </c>
       <c r="D225" s="14">
-        <f>IFERROR(VLOOKUP(A225,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A225,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.045045045045045</v>
       </c>
     </row>
@@ -29973,7 +29971,7 @@
         <v>22.328244274809162</v>
       </c>
       <c r="D226" s="14">
-        <f>IFERROR(VLOOKUP(A226,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A226,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>22.119815668202765</v>
       </c>
     </row>
@@ -29989,7 +29987,7 @@
         <v>16.304347826086957</v>
       </c>
       <c r="D227" s="14">
-        <f>IFERROR(VLOOKUP(A227,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A227,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>25.531914893617021</v>
       </c>
     </row>
@@ -30005,7 +30003,7 @@
         <v/>
       </c>
       <c r="D228" s="14">
-        <f>IFERROR(VLOOKUP(A228,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A228,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.4347826086956523</v>
       </c>
     </row>
@@ -30021,7 +30019,7 @@
         <v>9.5238095238095237</v>
       </c>
       <c r="D229" s="14">
-        <f>IFERROR(VLOOKUP(A229,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A229,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.634218289085545</v>
       </c>
     </row>
@@ -30037,7 +30035,7 @@
         <v>9.3761743705373917</v>
       </c>
       <c r="D230" s="14">
-        <f>IFERROR(VLOOKUP(A230,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A230,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>23.593890386343215</v>
       </c>
     </row>
@@ -30053,7 +30051,7 @@
         <v>13.92177969142447</v>
       </c>
       <c r="D231" s="14">
-        <f>IFERROR(VLOOKUP(A231,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A231,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.739403453689167</v>
       </c>
     </row>
@@ -30069,7 +30067,7 @@
         <v>26.81451612903226</v>
       </c>
       <c r="D232" s="14">
-        <f>IFERROR(VLOOKUP(A232,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A232,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>23.559870550161811</v>
       </c>
     </row>
@@ -30085,7 +30083,7 @@
         <v>7.934402508139395</v>
       </c>
       <c r="D233" s="14">
-        <f>IFERROR(VLOOKUP(A233,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A233,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.612093712380776</v>
       </c>
     </row>
@@ -30101,7 +30099,7 @@
         <v>13.327076489910841</v>
       </c>
       <c r="D234" s="14">
-        <f>IFERROR(VLOOKUP(A234,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A234,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>22.320794889992904</v>
       </c>
     </row>
@@ -30117,7 +30115,7 @@
         <v>4.8076923076923075</v>
       </c>
       <c r="D235" s="14">
-        <f>IFERROR(VLOOKUP(A235,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A235,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>17.278156996587029</v>
       </c>
     </row>
@@ -30133,7 +30131,7 @@
         <v/>
       </c>
       <c r="D236" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A236,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A236,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -30149,7 +30147,7 @@
         <v>21.178343949044585</v>
       </c>
       <c r="D237" s="14">
-        <f>IFERROR(VLOOKUP(A237,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A237,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.931034482758621</v>
       </c>
     </row>
@@ -30165,7 +30163,7 @@
         <v>19.174311926605505</v>
       </c>
       <c r="D238" s="14">
-        <f>IFERROR(VLOOKUP(A238,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A238,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.108831400535237</v>
       </c>
     </row>
@@ -30181,7 +30179,7 @@
         <v>25.523012552301257</v>
       </c>
       <c r="D239" s="14">
-        <f>IFERROR(VLOOKUP(A239,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A239,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>28.364779874213838</v>
       </c>
     </row>
@@ -30197,7 +30195,7 @@
         <v>40.705882352941174</v>
       </c>
       <c r="D240" s="14">
-        <f>IFERROR(VLOOKUP(A240,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A240,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>37.280701754385966</v>
       </c>
     </row>
@@ -30213,7 +30211,7 @@
         <v>4.4338875692794932</v>
       </c>
       <c r="D241" s="14">
-        <f>IFERROR(VLOOKUP(A241,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A241,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.9964584674822925</v>
       </c>
     </row>
@@ -30229,7 +30227,7 @@
         <v>12.444444444444445</v>
       </c>
       <c r="D242" s="14">
-        <f>IFERROR(VLOOKUP(A242,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A242,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.54043392504931</v>
       </c>
     </row>
@@ -30245,7 +30243,7 @@
         <v>4.3276905188893053</v>
       </c>
       <c r="D243" s="14">
-        <f>IFERROR(VLOOKUP(A243,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A243,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.750586099977312</v>
       </c>
     </row>
@@ -30261,7 +30259,7 @@
         <v>11.992309540975727</v>
       </c>
       <c r="D244" s="14">
-        <f>IFERROR(VLOOKUP(A244,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A244,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.972786508240706</v>
       </c>
     </row>
@@ -30277,7 +30275,7 @@
         <v>3.1675711595968545</v>
       </c>
       <c r="D245" s="14">
-        <f>IFERROR(VLOOKUP(A245,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A245,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.2810985460420028</v>
       </c>
     </row>
@@ -30293,7 +30291,7 @@
         <v>2.9177319897728982</v>
       </c>
       <c r="D246" s="14">
-        <f>IFERROR(VLOOKUP(A246,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A246,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.5169187033600506</v>
       </c>
     </row>
@@ -30309,7 +30307,7 @@
         <v>6.0862214708368558</v>
       </c>
       <c r="D247" s="14">
-        <f>IFERROR(VLOOKUP(A247,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A247,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.5173041894353378</v>
       </c>
     </row>
@@ -30325,7 +30323,7 @@
         <v>3.7666307083782811</v>
       </c>
       <c r="D248" s="14">
-        <f>IFERROR(VLOOKUP(A248,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A248,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.4389818953109614</v>
       </c>
     </row>
@@ -30341,7 +30339,7 @@
         <v>8.6583924349881798</v>
       </c>
       <c r="D249" s="14">
-        <f>IFERROR(VLOOKUP(A249,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A249,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.934441366574331</v>
       </c>
     </row>
@@ -30357,7 +30355,7 @@
         <v>4.7134935304990755</v>
       </c>
       <c r="D250" s="14">
-        <f>IFERROR(VLOOKUP(A250,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A250,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>29.20353982300885</v>
       </c>
     </row>
@@ -30373,7 +30371,7 @@
         <v>12.235799207397623</v>
       </c>
       <c r="D251" s="14">
-        <f>IFERROR(VLOOKUP(A251,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A251,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.141049671977507</v>
       </c>
     </row>
@@ -30389,7 +30387,7 @@
         <v>8.3365200764818361</v>
       </c>
       <c r="D252" s="14">
-        <f>IFERROR(VLOOKUP(A252,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A252,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>18.800813008130081</v>
       </c>
     </row>
@@ -30405,7 +30403,7 @@
         <v>8.1223628691983123</v>
       </c>
       <c r="D253" s="14">
-        <f>IFERROR(VLOOKUP(A253,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A253,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.955477738869435</v>
       </c>
     </row>
@@ -30421,7 +30419,7 @@
         <v>3.5991265485386368</v>
       </c>
       <c r="D254" s="14">
-        <f>IFERROR(VLOOKUP(A254,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A254,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.8348058108508747</v>
       </c>
     </row>
@@ -30437,7 +30435,7 @@
         <v>7.691011709207312</v>
       </c>
       <c r="D255" s="14">
-        <f>IFERROR(VLOOKUP(A255,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A255,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.596809980324025</v>
       </c>
     </row>
@@ -30453,7 +30451,7 @@
         <v>7.1809185485917277</v>
       </c>
       <c r="D256" s="14">
-        <f>IFERROR(VLOOKUP(A256,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A256,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.0119690213564887</v>
       </c>
     </row>
@@ -30469,7 +30467,7 @@
         <v>4.0807193132348756</v>
       </c>
       <c r="D257" s="14">
-        <f>IFERROR(VLOOKUP(A257,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A257,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.3467112049909122</v>
       </c>
     </row>
@@ -30485,7 +30483,7 @@
         <v>4.0084972753301926</v>
       </c>
       <c r="D258" s="14">
-        <f>IFERROR(VLOOKUP(A258,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A258,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.1685508735868444</v>
       </c>
     </row>
@@ -30501,7 +30499,7 @@
         <v>5.3154834541669658</v>
       </c>
       <c r="D259" s="14">
-        <f>IFERROR(VLOOKUP(A259,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A259,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.520409877372753</v>
       </c>
     </row>
@@ -30517,7 +30515,7 @@
         <v>4.6709129511677281</v>
       </c>
       <c r="D260" s="14">
-        <f>IFERROR(VLOOKUP(A260,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A260,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.415525114155251</v>
       </c>
     </row>
@@ -30533,7 +30531,7 @@
         <v>3.2555540030739136</v>
       </c>
       <c r="D261" s="14">
-        <f>IFERROR(VLOOKUP(A261,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A261,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.5138888888888893</v>
       </c>
     </row>
@@ -30549,7 +30547,7 @@
         <v>4.4419134396355355</v>
       </c>
       <c r="D262" s="14">
-        <f>IFERROR(VLOOKUP(A262,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A262,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.166666666666667</v>
       </c>
     </row>
@@ -30565,7 +30563,7 @@
         <v>5.9021922428330527</v>
       </c>
       <c r="D263" s="14">
-        <f>IFERROR(VLOOKUP(A263,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A263,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.5</v>
       </c>
     </row>
@@ -30581,7 +30579,7 @@
         <v>6.3859164653089406</v>
       </c>
       <c r="D264" s="14">
-        <f>IFERROR(VLOOKUP(A264,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A264,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.866261398176292</v>
       </c>
     </row>
@@ -30597,7 +30595,7 @@
         <v>5.0875273522975926</v>
       </c>
       <c r="D265" s="14">
-        <f>IFERROR(VLOOKUP(A265,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A265,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.2304366623432763</v>
       </c>
     </row>
@@ -30613,7 +30611,7 @@
         <v>4.490500863557858</v>
       </c>
       <c r="D266" s="14">
-        <f>IFERROR(VLOOKUP(A266,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A266,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.0935975158953131</v>
       </c>
     </row>
@@ -30629,7 +30627,7 @@
         <v>4.7730829420970267</v>
       </c>
       <c r="D267" s="14">
-        <f>IFERROR(VLOOKUP(A267,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A267,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.15417331206805</v>
       </c>
     </row>
@@ -30645,7 +30643,7 @@
         <v>3.8557993730407523</v>
       </c>
       <c r="D268" s="14">
-        <f>IFERROR(VLOOKUP(A268,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A268,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.382899628252789</v>
       </c>
     </row>
@@ -30661,7 +30659,7 @@
         <v>6.344628695025234</v>
       </c>
       <c r="D269" s="14">
-        <f>IFERROR(VLOOKUP(A269,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A269,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.0405904059040587</v>
       </c>
     </row>
@@ -30677,7 +30675,7 @@
         <v>4.5212765957446805</v>
       </c>
       <c r="D270" s="14">
-        <f>IFERROR(VLOOKUP(A270,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A270,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.821086261980831</v>
       </c>
     </row>
@@ -30693,7 +30691,7 @@
         <v>2.6385224274406331</v>
       </c>
       <c r="D271" s="14">
-        <f>IFERROR(VLOOKUP(A271,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A271,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>6.11740473738414</v>
       </c>
     </row>
@@ -30709,7 +30707,7 @@
         <v>6.7304286220332976</v>
       </c>
       <c r="D272" s="14">
-        <f>IFERROR(VLOOKUP(A272,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A272,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.043753294675804</v>
       </c>
     </row>
@@ -30725,7 +30723,7 @@
         <v>4.791666666666667</v>
       </c>
       <c r="D273" s="14">
-        <f>IFERROR(VLOOKUP(A273,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A273,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.914543960558751</v>
       </c>
     </row>
@@ -30741,7 +30739,7 @@
         <v>3.2509752925877762</v>
       </c>
       <c r="D274" s="14">
-        <f>IFERROR(VLOOKUP(A274,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A274,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.64367816091954</v>
       </c>
     </row>
@@ -30757,7 +30755,7 @@
         <v>5.2793664760228776</v>
       </c>
       <c r="D275" s="14">
-        <f>IFERROR(VLOOKUP(A275,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A275,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>13.48747591522158</v>
       </c>
     </row>
@@ -30773,7 +30771,7 @@
         <v>7.0765289785462695</v>
       </c>
       <c r="D276" s="14">
-        <f>IFERROR(VLOOKUP(A276,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A276,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.672762066765895</v>
       </c>
     </row>
@@ -30789,7 +30787,7 @@
         <v>5.1908396946564883</v>
       </c>
       <c r="D277" s="14">
-        <f>IFERROR(VLOOKUP(A277,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A277,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.727272727272727</v>
       </c>
     </row>
@@ -30805,7 +30803,7 @@
         <v>3.4653465346534653</v>
       </c>
       <c r="D278" s="14">
-        <f>IFERROR(VLOOKUP(A278,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A278,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15</v>
       </c>
     </row>
@@ -30821,7 +30819,7 @@
         <v>2.8701107996262181</v>
       </c>
       <c r="D279" s="14">
-        <f>IFERROR(VLOOKUP(A279,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A279,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.6650246305418719</v>
       </c>
     </row>
@@ -30837,7 +30835,7 @@
         <v>3.7220843672456576</v>
       </c>
       <c r="D280" s="14">
-        <f>IFERROR(VLOOKUP(A280,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A280,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.160714285714286</v>
       </c>
     </row>
@@ -30853,7 +30851,7 @@
         <v>6.7956795679567961</v>
       </c>
       <c r="D281" s="14">
-        <f>IFERROR(VLOOKUP(A281,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A281,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.8235294117647065</v>
       </c>
     </row>
@@ -30869,7 +30867,7 @@
         <v>5.9615384615384617</v>
       </c>
       <c r="D282" s="14">
-        <f>IFERROR(VLOOKUP(A282,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A282,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>20.833333333333332</v>
       </c>
     </row>
@@ -30885,7 +30883,7 @@
         <v>5.882352941176471</v>
       </c>
       <c r="D283" s="14">
-        <f>IFERROR(VLOOKUP(A283,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A283,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.0909090909090917</v>
       </c>
     </row>
@@ -30901,7 +30899,7 @@
         <v>11.797752808988765</v>
       </c>
       <c r="D284" s="14">
-        <f>IFERROR(VLOOKUP(A284,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A284,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>43.75</v>
       </c>
     </row>
@@ -30917,7 +30915,7 @@
         <v/>
       </c>
       <c r="D285" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A285,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A285,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -30933,7 +30931,7 @@
         <v>7.1120689655172411</v>
       </c>
       <c r="D286" s="14">
-        <f>IFERROR(VLOOKUP(A286,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A286,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.373225152129818</v>
       </c>
     </row>
@@ -30949,7 +30947,7 @@
         <v>6.8231203824424167</v>
       </c>
       <c r="D287" s="14">
-        <f>IFERROR(VLOOKUP(A287,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A287,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.6363636363636367</v>
       </c>
     </row>
@@ -30965,7 +30963,7 @@
         <v>5.2201012855473312</v>
       </c>
       <c r="D288" s="14">
-        <f>IFERROR(VLOOKUP(A288,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A288,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.76923076923077</v>
       </c>
     </row>
@@ -30981,7 +30979,7 @@
         <v>10.591133004926109</v>
       </c>
       <c r="D289" s="14">
-        <f>IFERROR(VLOOKUP(A289,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A289,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.3170731707317076</v>
       </c>
     </row>
@@ -30997,7 +30995,7 @@
         <v>3.1306940533377507</v>
       </c>
       <c r="D290" s="14">
-        <f>IFERROR(VLOOKUP(A290,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A290,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.7428526792688643</v>
       </c>
     </row>
@@ -31013,7 +31011,7 @@
         <v>5.8174904942965782</v>
       </c>
       <c r="D291" s="14">
-        <f>IFERROR(VLOOKUP(A291,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A291,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.285538839422781</v>
       </c>
     </row>
@@ -31029,7 +31027,7 @@
         <v>3.7574316290130798</v>
       </c>
       <c r="D292" s="14">
-        <f>IFERROR(VLOOKUP(A292,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A292,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.5535512965050735</v>
       </c>
     </row>
@@ -31045,7 +31043,7 @@
         <v>5.0700741962077496</v>
       </c>
       <c r="D293" s="14">
-        <f>IFERROR(VLOOKUP(A293,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A293,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.9802955665024626</v>
       </c>
     </row>
@@ -31061,7 +31059,7 @@
         <v>5.1418439716312054</v>
       </c>
       <c r="D294" s="14">
-        <f>IFERROR(VLOOKUP(A294,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A294,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.4931145619689428</v>
       </c>
     </row>
@@ -31077,7 +31075,7 @@
         <v>5.2973675658108546</v>
       </c>
       <c r="D295" s="14">
-        <f>IFERROR(VLOOKUP(A295,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A295,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.185308848080133</v>
       </c>
     </row>
@@ -31093,7 +31091,7 @@
         <v>3.8436050364479786</v>
       </c>
       <c r="D296" s="14">
-        <f>IFERROR(VLOOKUP(A296,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A296,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>15.527950310559007</v>
       </c>
     </row>
@@ -31109,7 +31107,7 @@
         <v>3.7828947368421053</v>
       </c>
       <c r="D297" s="14">
-        <f>IFERROR(VLOOKUP(A297,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A297,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>11.728395061728396</v>
       </c>
     </row>
@@ -31125,7 +31123,7 @@
         <v>4.9664075879330785</v>
       </c>
       <c r="D298" s="14">
-        <f>IFERROR(VLOOKUP(A298,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A298,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.8332234673698089</v>
       </c>
     </row>
@@ -31141,7 +31139,7 @@
         <v>2.8907922912205568</v>
       </c>
       <c r="D299" s="14">
-        <f>IFERROR(VLOOKUP(A299,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A299,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.5890410958904102</v>
       </c>
     </row>
@@ -31157,7 +31155,7 @@
         <v>5.2769070010449317</v>
       </c>
       <c r="D300" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A300,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A300,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31173,7 +31171,7 @@
         <v>0</v>
       </c>
       <c r="D301" s="14">
-        <f>IFERROR(VLOOKUP(A301,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A301,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -31189,7 +31187,7 @@
         <v>5.3119730185497467</v>
       </c>
       <c r="D302" s="14">
-        <f>IFERROR(VLOOKUP(A302,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A302,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>8.8888888888888893</v>
       </c>
     </row>
@@ -31205,7 +31203,7 @@
         <v>8.8871715610510051</v>
       </c>
       <c r="D303" s="14">
-        <f>IFERROR(VLOOKUP(A303,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A303,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>10.476190476190476</v>
       </c>
     </row>
@@ -31221,7 +31219,7 @@
         <v>7.3772514187021958</v>
       </c>
       <c r="D304" s="14">
-        <f>IFERROR(VLOOKUP(A304,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A304,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>9.7276264591439681</v>
       </c>
     </row>
@@ -31237,7 +31235,7 @@
         <v>5.7947468183049011</v>
       </c>
       <c r="D305" s="14">
-        <f>IFERROR(VLOOKUP(A305,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A305,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.6271186440677967</v>
       </c>
     </row>
@@ -31253,7 +31251,7 @@
         <v>3.9951573849878934</v>
       </c>
       <c r="D306" s="14">
-        <f>IFERROR(VLOOKUP(A306,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A306,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>7.5</v>
       </c>
     </row>
@@ -31269,7 +31267,7 @@
         <v>4.1925823542962455</v>
       </c>
       <c r="D307" s="14">
-        <f>IFERROR(VLOOKUP(A307,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A307,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>12.816455696202532</v>
       </c>
     </row>
@@ -31285,7 +31283,7 @@
         <v>5.162738496071829</v>
       </c>
       <c r="D308" s="14">
-        <f>IFERROR(VLOOKUP(A308,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A308,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>20</v>
       </c>
     </row>
@@ -31301,7 +31299,7 @@
         <v>6.2796208530805684</v>
       </c>
       <c r="D309" s="14">
-        <f>IFERROR(VLOOKUP(A309,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A309,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>14.64968152866242</v>
       </c>
     </row>
@@ -31317,7 +31315,7 @@
         <v>1.2784368457780879</v>
       </c>
       <c r="D310" s="14">
-        <f>IFERROR(VLOOKUP(A310,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A310,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>1.2237498111497205</v>
       </c>
     </row>
@@ -31333,7 +31331,7 @@
         <v>4.3795620437956204</v>
       </c>
       <c r="D311" s="14">
-        <f>IFERROR(VLOOKUP(A311,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A311,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>4.4776119402985071</v>
       </c>
     </row>
@@ -31349,7 +31347,7 @@
         <v>0</v>
       </c>
       <c r="D312" s="14">
-        <f>IFERROR(VLOOKUP(A312,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A312,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>1.658310836868492</v>
       </c>
     </row>
@@ -31365,7 +31363,7 @@
         <v>0</v>
       </c>
       <c r="D313" s="14">
-        <f>IFERROR(VLOOKUP(A313,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A313,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0.76475657044377421</v>
       </c>
     </row>
@@ -31381,7 +31379,7 @@
         <v>0.72337962962962965</v>
       </c>
       <c r="D314" s="14">
-        <f>IFERROR(VLOOKUP(A314,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A314,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.0727519204699503</v>
       </c>
     </row>
@@ -31397,7 +31395,7 @@
         <v>1.4986274946212628</v>
       </c>
       <c r="D315" s="14">
-        <f>IFERROR(VLOOKUP(A315,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A315,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.2360930672020785</v>
       </c>
     </row>
@@ -31413,7 +31411,7 @@
         <v>0.14306151645207441</v>
       </c>
       <c r="D316" s="14">
-        <f>IFERROR(VLOOKUP(A316,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A316,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.0318870883429168</v>
       </c>
     </row>
@@ -31429,7 +31427,7 @@
         <v>1.113916530521313</v>
       </c>
       <c r="D317" s="14">
-        <f>IFERROR(VLOOKUP(A317,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A317,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.5487269534679546</v>
       </c>
     </row>
@@ -31445,7 +31443,7 @@
         <v>6.5608187901850148E-2</v>
       </c>
       <c r="D318" s="14">
-        <f>IFERROR(VLOOKUP(A318,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A318,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>2.2270337148159602</v>
       </c>
     </row>
@@ -31461,7 +31459,7 @@
         <v/>
       </c>
       <c r="D319" s="14">
-        <f>IFERROR(VLOOKUP(A319,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A319,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -31477,7 +31475,7 @@
         <v>0.54294862870666849</v>
       </c>
       <c r="D320" s="14">
-        <f>IFERROR(VLOOKUP(A320,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A320,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>2.7903043968432919</v>
       </c>
     </row>
@@ -31493,7 +31491,7 @@
         <v>2.3391812865497075</v>
       </c>
       <c r="D321" s="14">
-        <f>IFERROR(VLOOKUP(A321,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A321,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.7142857142857144</v>
       </c>
     </row>
@@ -31509,7 +31507,7 @@
         <v>3.2432432432432434</v>
       </c>
       <c r="D322" s="14">
-        <f>IFERROR(VLOOKUP(A322,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A322,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>5.6306306306306304</v>
       </c>
     </row>
@@ -31525,7 +31523,7 @@
         <v>0.86058519793459554</v>
       </c>
       <c r="D323" s="14">
-        <f>IFERROR(VLOOKUP(A323,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A323,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>1.2583892617449663</v>
       </c>
     </row>
@@ -31541,7 +31539,7 @@
         <v>2.2529069767441858</v>
       </c>
       <c r="D324" s="14">
-        <f>IFERROR(VLOOKUP(A324,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A324,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>2.15962441314554</v>
       </c>
     </row>
@@ -31557,7 +31555,7 @@
         <v/>
       </c>
       <c r="D325" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A325,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A325,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31573,7 +31571,7 @@
         <v>0.32530904359141183</v>
       </c>
       <c r="D326" s="14">
-        <f>IFERROR(VLOOKUP(A326,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A326,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>1.6483516483516483</v>
       </c>
     </row>
@@ -31589,7 +31587,7 @@
         <v>0</v>
       </c>
       <c r="D327" s="14">
-        <f>IFERROR(VLOOKUP(A327,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A327,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>1.392515230635335</v>
       </c>
     </row>
@@ -31605,7 +31603,7 @@
         <v>0</v>
       </c>
       <c r="D328" s="14">
-        <f>IFERROR(VLOOKUP(A328,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A328,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>0.95923261390887293</v>
       </c>
     </row>
@@ -31621,7 +31619,7 @@
         <v/>
       </c>
       <c r="D329" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A329,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A329,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31637,7 +31635,7 @@
         <v>2.0263942103022563</v>
       </c>
       <c r="D330" s="14">
-        <f>IFERROR(VLOOKUP(A330,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A330,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>1.7314300819455459</v>
       </c>
     </row>
@@ -31653,7 +31651,7 @@
         <v>3.5126234906695939</v>
       </c>
       <c r="D331" s="14">
-        <f>IFERROR(VLOOKUP(A331,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A331,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.0927835051546393</v>
       </c>
     </row>
@@ -31669,7 +31667,7 @@
         <v/>
       </c>
       <c r="D332" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A332,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A332,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31685,7 +31683,7 @@
         <v>0.49504950495049505</v>
       </c>
       <c r="D333" s="14">
-        <f>IFERROR(VLOOKUP(A333,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A333,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.6613272311212817</v>
       </c>
     </row>
@@ -31701,7 +31699,7 @@
         <v>4.1884816753926701</v>
       </c>
       <c r="D334" s="14">
-        <f>IFERROR(VLOOKUP(A334,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A334,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>3.0473135525260626</v>
       </c>
     </row>
@@ -31717,7 +31715,7 @@
         <v>2.9411764705882355</v>
       </c>
       <c r="D335" s="14">
-        <f>IFERROR(VLOOKUP(A335,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A335,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v>2.5806451612903225</v>
       </c>
     </row>
@@ -31732,9 +31730,9 @@
         <f>IFERROR(VLOOKUP(A336,datos_2016!$B$1:$G$330,6,FALSE),"")</f>
         <v>3.9603960396039604</v>
       </c>
-      <c r="D336" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A336,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
-        <v/>
+      <c r="D336" s="14">
+        <f>IFERROR(VLOOKUP(A336,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
+        <v>3.8043478260869565</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -31749,7 +31747,7 @@
         <v>0</v>
       </c>
       <c r="D337" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A337,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A337,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31764,9 +31762,9 @@
         <f>IFERROR(VLOOKUP(A338,datos_2016!$B$1:$G$330,6,FALSE),"")</f>
         <v>0.5376344086021505</v>
       </c>
-      <c r="D338" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A338,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
-        <v/>
+      <c r="D338" s="14">
+        <f>IFERROR(VLOOKUP(A338,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
+        <v>1.3205282112845138</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -31780,9 +31778,9 @@
         <f>IFERROR(VLOOKUP(A339,datos_2016!$B$1:$G$330,6,FALSE),"")</f>
         <v>0.39920159680638723</v>
       </c>
-      <c r="D339" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A339,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
-        <v/>
+      <c r="D339" s="14">
+        <f>IFERROR(VLOOKUP(A339,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
+        <v>1.9981834695731153</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -31796,9 +31794,9 @@
         <f>IFERROR(VLOOKUP(A340,datos_2016!$B$1:$G$330,6,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D340" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A340,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
-        <v/>
+      <c r="D340" s="14">
+        <f>IFERROR(VLOOKUP(A340,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
+        <v>7.1428571428571432</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -31813,7 +31811,7 @@
         <v/>
       </c>
       <c r="D341" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A341,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A341,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31829,7 +31827,7 @@
         <v>0</v>
       </c>
       <c r="D342" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A342,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A342,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31845,7 +31843,7 @@
         <v>0</v>
       </c>
       <c r="D343" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A343,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A343,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31861,7 +31859,7 @@
         <v/>
       </c>
       <c r="D344" s="14" t="str">
-        <f>IFERROR(VLOOKUP(A344,datos_2024!$B$1:$G$322,6,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A344,datos_2024!$B$1:$G$342,6,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -31905,7 +31903,7 @@
         <v>2422</v>
       </c>
       <c r="D2" s="21">
-        <f>IFERROR(VLOOKUP(A2,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A2,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>5007</v>
       </c>
     </row>
@@ -31921,7 +31919,7 @@
         <v>281</v>
       </c>
       <c r="D3" s="21">
-        <f>IFERROR(VLOOKUP(A3,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A3,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>492</v>
       </c>
     </row>
@@ -31937,7 +31935,7 @@
         <v>139</v>
       </c>
       <c r="D4" s="21">
-        <f>IFERROR(VLOOKUP(A4,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A4,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>300</v>
       </c>
     </row>
@@ -31953,7 +31951,7 @@
         <v>81</v>
       </c>
       <c r="D5" s="21">
-        <f>IFERROR(VLOOKUP(A5,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A5,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>239</v>
       </c>
     </row>
@@ -31969,7 +31967,7 @@
         <v>198</v>
       </c>
       <c r="D6" s="21">
-        <f>IFERROR(VLOOKUP(A6,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A6,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>358</v>
       </c>
     </row>
@@ -31985,7 +31983,7 @@
         <v>149</v>
       </c>
       <c r="D7" s="21">
-        <f>IFERROR(VLOOKUP(A7,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A7,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>265</v>
       </c>
     </row>
@@ -32001,7 +31999,7 @@
         <v>86</v>
       </c>
       <c r="D8" s="21">
-        <f>IFERROR(VLOOKUP(A8,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A8,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>116</v>
       </c>
     </row>
@@ -32017,7 +32015,7 @@
         <v>121</v>
       </c>
       <c r="D9" s="21">
-        <f>IFERROR(VLOOKUP(A9,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A9,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>211</v>
       </c>
     </row>
@@ -32033,7 +32031,7 @@
         <v>137</v>
       </c>
       <c r="D10" s="21">
-        <f>IFERROR(VLOOKUP(A10,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A10,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>156</v>
       </c>
     </row>
@@ -32049,7 +32047,7 @@
         <v>158</v>
       </c>
       <c r="D11" s="21">
-        <f>IFERROR(VLOOKUP(A11,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A11,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>300</v>
       </c>
     </row>
@@ -32065,7 +32063,7 @@
         <v>125</v>
       </c>
       <c r="D12" s="21">
-        <f>IFERROR(VLOOKUP(A12,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A12,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>256</v>
       </c>
     </row>
@@ -32081,7 +32079,7 @@
         <v>40</v>
       </c>
       <c r="D13" s="21">
-        <f>IFERROR(VLOOKUP(A13,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A13,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>216</v>
       </c>
     </row>
@@ -32097,7 +32095,7 @@
         <v>85</v>
       </c>
       <c r="D14" s="21">
-        <f>IFERROR(VLOOKUP(A14,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A14,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>167</v>
       </c>
     </row>
@@ -32113,7 +32111,7 @@
         <v>176</v>
       </c>
       <c r="D15" s="21">
-        <f>IFERROR(VLOOKUP(A15,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A15,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>143</v>
       </c>
     </row>
@@ -32129,7 +32127,7 @@
         <v>183</v>
       </c>
       <c r="D16" s="21">
-        <f>IFERROR(VLOOKUP(A16,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A16,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>412</v>
       </c>
     </row>
@@ -32145,7 +32143,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="21">
-        <f>IFERROR(VLOOKUP(A17,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A17,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>150</v>
       </c>
     </row>
@@ -32161,7 +32159,7 @@
         <v>212</v>
       </c>
       <c r="D18" s="21">
-        <f>IFERROR(VLOOKUP(A18,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A18,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>580</v>
       </c>
     </row>
@@ -32177,7 +32175,7 @@
         <v>198</v>
       </c>
       <c r="D19" s="21">
-        <f>IFERROR(VLOOKUP(A19,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A19,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>402</v>
       </c>
     </row>
@@ -32193,7 +32191,7 @@
         <v>385</v>
       </c>
       <c r="D20" s="21">
-        <f>IFERROR(VLOOKUP(A20,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A20,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>719</v>
       </c>
     </row>
@@ -32209,7 +32207,7 @@
         <v>670</v>
       </c>
       <c r="D21" s="21">
-        <f>IFERROR(VLOOKUP(A21,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A21,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1677</v>
       </c>
     </row>
@@ -32225,7 +32223,7 @@
         <v>73</v>
       </c>
       <c r="D22" s="21">
-        <f>IFERROR(VLOOKUP(A22,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A22,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>153</v>
       </c>
     </row>
@@ -32241,7 +32239,7 @@
         <v>173</v>
       </c>
       <c r="D23" s="21">
-        <f>IFERROR(VLOOKUP(A23,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A23,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>357</v>
       </c>
     </row>
@@ -32257,7 +32255,7 @@
         <v>244</v>
       </c>
       <c r="D24" s="21">
-        <f>IFERROR(VLOOKUP(A24,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A24,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>524</v>
       </c>
     </row>
@@ -32273,7 +32271,7 @@
         <v>98</v>
       </c>
       <c r="D25" s="21">
-        <f>IFERROR(VLOOKUP(A25,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A25,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>191</v>
       </c>
     </row>
@@ -32289,7 +32287,7 @@
         <v>203</v>
       </c>
       <c r="D26" s="21">
-        <f>IFERROR(VLOOKUP(A26,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A26,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>295</v>
       </c>
     </row>
@@ -32305,7 +32303,7 @@
         <v>89</v>
       </c>
       <c r="D27" s="21">
-        <f>IFERROR(VLOOKUP(A27,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A27,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>190</v>
       </c>
     </row>
@@ -32321,7 +32319,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="21">
-        <f>IFERROR(VLOOKUP(A28,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A28,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>115</v>
       </c>
     </row>
@@ -32337,7 +32335,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="21">
-        <f>IFERROR(VLOOKUP(A29,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A29,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>8</v>
       </c>
     </row>
@@ -32353,7 +32351,7 @@
         <v>55</v>
       </c>
       <c r="D30" s="21">
-        <f>IFERROR(VLOOKUP(A30,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A30,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>71</v>
       </c>
     </row>
@@ -32369,7 +32367,7 @@
         <v>11026</v>
       </c>
       <c r="D31" s="21">
-        <f>IFERROR(VLOOKUP(A31,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A31,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>18660</v>
       </c>
     </row>
@@ -32385,7 +32383,7 @@
         <v>317</v>
       </c>
       <c r="D32" s="21">
-        <f>IFERROR(VLOOKUP(A32,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A32,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>408</v>
       </c>
     </row>
@@ -32401,7 +32399,7 @@
         <v>468</v>
       </c>
       <c r="D33" s="21">
-        <f>IFERROR(VLOOKUP(A33,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A33,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>873</v>
       </c>
     </row>
@@ -32417,7 +32415,7 @@
         <v>780</v>
       </c>
       <c r="D34" s="21">
-        <f>IFERROR(VLOOKUP(A34,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A34,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>2068</v>
       </c>
     </row>
@@ -32433,7 +32431,7 @@
         <v>20483</v>
       </c>
       <c r="D35" s="21">
-        <f>IFERROR(VLOOKUP(A35,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A35,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>23131</v>
       </c>
     </row>
@@ -32449,7 +32447,7 @@
         <v>1705</v>
       </c>
       <c r="D36" s="21">
-        <f>IFERROR(VLOOKUP(A36,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A36,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1712</v>
       </c>
     </row>
@@ -32465,7 +32463,7 @@
         <v>690</v>
       </c>
       <c r="D37" s="21">
-        <f>IFERROR(VLOOKUP(A37,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A37,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>544</v>
       </c>
     </row>
@@ -32481,7 +32479,7 @@
         <v>238</v>
       </c>
       <c r="D38" s="21">
-        <f>IFERROR(VLOOKUP(A38,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A38,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>216</v>
       </c>
     </row>
@@ -32497,7 +32495,7 @@
         <v>472</v>
       </c>
       <c r="D39" s="21">
-        <f>IFERROR(VLOOKUP(A39,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A39,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>356</v>
       </c>
     </row>
@@ -32513,7 +32511,7 @@
         <v>529</v>
       </c>
       <c r="D40" s="21">
-        <f>IFERROR(VLOOKUP(A40,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A40,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>608</v>
       </c>
     </row>
@@ -32529,7 +32527,7 @@
         <v>260</v>
       </c>
       <c r="D41" s="21">
-        <f>IFERROR(VLOOKUP(A41,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A41,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>258</v>
       </c>
     </row>
@@ -32545,7 +32543,7 @@
         <v>763</v>
       </c>
       <c r="D42" s="21">
-        <f>IFERROR(VLOOKUP(A42,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A42,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>759</v>
       </c>
     </row>
@@ -32561,7 +32559,7 @@
         <v>914</v>
       </c>
       <c r="D43" s="21">
-        <f>IFERROR(VLOOKUP(A43,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A43,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>987</v>
       </c>
     </row>
@@ -32577,7 +32575,7 @@
         <v>347</v>
       </c>
       <c r="D44" s="21">
-        <f>IFERROR(VLOOKUP(A44,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A44,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>560</v>
       </c>
     </row>
@@ -32593,7 +32591,7 @@
         <v>194</v>
       </c>
       <c r="D45" s="21">
-        <f>IFERROR(VLOOKUP(A45,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A45,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>306</v>
       </c>
     </row>
@@ -32609,7 +32607,7 @@
         <v>61</v>
       </c>
       <c r="D46" s="21">
-        <f>IFERROR(VLOOKUP(A46,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A46,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>65</v>
       </c>
     </row>
@@ -32625,7 +32623,7 @@
         <v>63</v>
       </c>
       <c r="D47" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A47,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A47,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -32641,7 +32639,7 @@
         <v>17</v>
       </c>
       <c r="D48" s="21">
-        <f>IFERROR(VLOOKUP(A48,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A48,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>24</v>
       </c>
     </row>
@@ -32657,7 +32655,7 @@
         <v>205</v>
       </c>
       <c r="D49" s="21">
-        <f>IFERROR(VLOOKUP(A49,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A49,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>526</v>
       </c>
     </row>
@@ -32673,7 +32671,7 @@
         <v>571</v>
       </c>
       <c r="D50" s="21">
-        <f>IFERROR(VLOOKUP(A50,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A50,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>618</v>
       </c>
     </row>
@@ -32689,7 +32687,7 @@
         <v>436</v>
       </c>
       <c r="D51" s="21">
-        <f>IFERROR(VLOOKUP(A51,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A51,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>401</v>
       </c>
     </row>
@@ -32705,7 +32703,7 @@
         <v>550</v>
       </c>
       <c r="D52" s="21">
-        <f>IFERROR(VLOOKUP(A52,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A52,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>481</v>
       </c>
     </row>
@@ -32721,7 +32719,7 @@
         <v>138</v>
       </c>
       <c r="D53" s="21">
-        <f>IFERROR(VLOOKUP(A53,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A53,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>114</v>
       </c>
     </row>
@@ -32737,7 +32735,7 @@
         <v>294</v>
       </c>
       <c r="D54" s="21">
-        <f>IFERROR(VLOOKUP(A54,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A54,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>230</v>
       </c>
     </row>
@@ -32753,7 +32751,7 @@
         <v>424</v>
       </c>
       <c r="D55" s="21">
-        <f>IFERROR(VLOOKUP(A55,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A55,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>463</v>
       </c>
     </row>
@@ -32769,7 +32767,7 @@
         <v>161</v>
       </c>
       <c r="D56" s="21">
-        <f>IFERROR(VLOOKUP(A56,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A56,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>197</v>
       </c>
     </row>
@@ -32785,7 +32783,7 @@
         <v>140</v>
       </c>
       <c r="D57" s="21">
-        <f>IFERROR(VLOOKUP(A57,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A57,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>108</v>
       </c>
     </row>
@@ -32801,7 +32799,7 @@
         <v>1022</v>
       </c>
       <c r="D58" s="21">
-        <f>IFERROR(VLOOKUP(A58,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A58,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>799</v>
       </c>
     </row>
@@ -32817,7 +32815,7 @@
         <v>178</v>
       </c>
       <c r="D59" s="21">
-        <f>IFERROR(VLOOKUP(A59,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A59,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>96</v>
       </c>
     </row>
@@ -32833,7 +32831,7 @@
         <v>205</v>
       </c>
       <c r="D60" s="21">
-        <f>IFERROR(VLOOKUP(A60,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A60,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>241</v>
       </c>
     </row>
@@ -32849,7 +32847,7 @@
         <v>121</v>
       </c>
       <c r="D61" s="21">
-        <f>IFERROR(VLOOKUP(A61,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A61,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>74</v>
       </c>
     </row>
@@ -32865,7 +32863,7 @@
         <v>147</v>
       </c>
       <c r="D62" s="21">
-        <f>IFERROR(VLOOKUP(A62,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A62,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>101</v>
       </c>
     </row>
@@ -32881,7 +32879,7 @@
         <v>163</v>
       </c>
       <c r="D63" s="21">
-        <f>IFERROR(VLOOKUP(A63,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A63,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>134</v>
       </c>
     </row>
@@ -32897,7 +32895,7 @@
         <v>93</v>
       </c>
       <c r="D64" s="21">
-        <f>IFERROR(VLOOKUP(A64,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A64,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>155</v>
       </c>
     </row>
@@ -32913,7 +32911,7 @@
         <v>115</v>
       </c>
       <c r="D65" s="21">
-        <f>IFERROR(VLOOKUP(A65,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A65,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>232</v>
       </c>
     </row>
@@ -32929,7 +32927,7 @@
         <v>257</v>
       </c>
       <c r="D66" s="21">
-        <f>IFERROR(VLOOKUP(A66,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A66,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>315</v>
       </c>
     </row>
@@ -32945,7 +32943,7 @@
         <v>141</v>
       </c>
       <c r="D67" s="21">
-        <f>IFERROR(VLOOKUP(A67,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A67,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>166</v>
       </c>
     </row>
@@ -32961,7 +32959,7 @@
         <v>4253</v>
       </c>
       <c r="D68" s="21">
-        <f>IFERROR(VLOOKUP(A68,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A68,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>6469</v>
       </c>
     </row>
@@ -32977,7 +32975,7 @@
         <v>687</v>
       </c>
       <c r="D69" s="21">
-        <f>IFERROR(VLOOKUP(A69,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A69,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>525</v>
       </c>
     </row>
@@ -32993,7 +32991,7 @@
         <v>492</v>
       </c>
       <c r="D70" s="21">
-        <f>IFERROR(VLOOKUP(A70,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A70,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>546</v>
       </c>
     </row>
@@ -33009,7 +33007,7 @@
         <v>387</v>
       </c>
       <c r="D71" s="21">
-        <f>IFERROR(VLOOKUP(A71,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A71,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>258</v>
       </c>
     </row>
@@ -33025,7 +33023,7 @@
         <v>330</v>
       </c>
       <c r="D72" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A72,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A72,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -33041,7 +33039,7 @@
         <v>581</v>
       </c>
       <c r="D73" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A73,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A73,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -33057,7 +33055,7 @@
         <v>318</v>
       </c>
       <c r="D74" s="21">
-        <f>IFERROR(VLOOKUP(A74,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A74,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>366</v>
       </c>
     </row>
@@ -33073,7 +33071,7 @@
         <v>355</v>
       </c>
       <c r="D75" s="21">
-        <f>IFERROR(VLOOKUP(A75,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A75,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>308</v>
       </c>
     </row>
@@ -33089,7 +33087,7 @@
         <v>492</v>
       </c>
       <c r="D76" s="21">
-        <f>IFERROR(VLOOKUP(A76,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A76,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>398</v>
       </c>
     </row>
@@ -33105,7 +33103,7 @@
         <v>346</v>
       </c>
       <c r="D77" s="21">
-        <f>IFERROR(VLOOKUP(A77,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A77,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>231</v>
       </c>
     </row>
@@ -33121,7 +33119,7 @@
         <v>72</v>
       </c>
       <c r="D78" s="21">
-        <f>IFERROR(VLOOKUP(A78,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A78,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>32</v>
       </c>
     </row>
@@ -33137,7 +33135,7 @@
         <v>452</v>
       </c>
       <c r="D79" s="21">
-        <f>IFERROR(VLOOKUP(A79,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A79,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>98</v>
       </c>
     </row>
@@ -33153,7 +33151,7 @@
         <v>264</v>
       </c>
       <c r="D80" s="21">
-        <f>IFERROR(VLOOKUP(A80,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A80,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>273</v>
       </c>
     </row>
@@ -33169,7 +33167,7 @@
         <v>120</v>
       </c>
       <c r="D81" s="21">
-        <f>IFERROR(VLOOKUP(A81,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A81,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>177</v>
       </c>
     </row>
@@ -33185,7 +33183,7 @@
         <v>273</v>
       </c>
       <c r="D82" s="21">
-        <f>IFERROR(VLOOKUP(A82,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A82,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>144</v>
       </c>
     </row>
@@ -33201,7 +33199,7 @@
         <v>530</v>
       </c>
       <c r="D83" s="21">
-        <f>IFERROR(VLOOKUP(A83,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A83,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>345</v>
       </c>
     </row>
@@ -33217,7 +33215,7 @@
         <v>352</v>
       </c>
       <c r="D84" s="21">
-        <f>IFERROR(VLOOKUP(A84,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A84,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>144</v>
       </c>
     </row>
@@ -33233,7 +33231,7 @@
         <v>69</v>
       </c>
       <c r="D85" s="21">
-        <f>IFERROR(VLOOKUP(A85,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A85,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>65</v>
       </c>
     </row>
@@ -33249,7 +33247,7 @@
         <v>265</v>
       </c>
       <c r="D86" s="21">
-        <f>IFERROR(VLOOKUP(A86,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A86,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>385</v>
       </c>
     </row>
@@ -33265,7 +33263,7 @@
         <v>328</v>
       </c>
       <c r="D87" s="21">
-        <f>IFERROR(VLOOKUP(A87,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A87,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>417</v>
       </c>
     </row>
@@ -33281,7 +33279,7 @@
         <v>75</v>
       </c>
       <c r="D88" s="21">
-        <f>IFERROR(VLOOKUP(A88,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A88,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>124</v>
       </c>
     </row>
@@ -33297,7 +33295,7 @@
         <v>696</v>
       </c>
       <c r="D89" s="21">
-        <f>IFERROR(VLOOKUP(A89,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A89,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>559</v>
       </c>
     </row>
@@ -33313,7 +33311,7 @@
         <v>350</v>
       </c>
       <c r="D90" s="21">
-        <f>IFERROR(VLOOKUP(A90,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A90,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>875</v>
       </c>
     </row>
@@ -33329,7 +33327,7 @@
         <v>1188</v>
       </c>
       <c r="D91" s="21">
-        <f>IFERROR(VLOOKUP(A91,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A91,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>4395</v>
       </c>
     </row>
@@ -33345,7 +33343,7 @@
         <v>937</v>
       </c>
       <c r="D92" s="21">
-        <f>IFERROR(VLOOKUP(A92,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A92,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1568</v>
       </c>
     </row>
@@ -33361,7 +33359,7 @@
         <v>741</v>
       </c>
       <c r="D93" s="21">
-        <f>IFERROR(VLOOKUP(A93,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A93,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>630</v>
       </c>
     </row>
@@ -33377,7 +33375,7 @@
         <v>256</v>
       </c>
       <c r="D94" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A94,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A94,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -33393,7 +33391,7 @@
         <v>1032</v>
       </c>
       <c r="D95" s="21">
-        <f>IFERROR(VLOOKUP(A95,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A95,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>788</v>
       </c>
     </row>
@@ -33409,7 +33407,7 @@
         <v>632</v>
       </c>
       <c r="D96" s="21">
-        <f>IFERROR(VLOOKUP(A96,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A96,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>688</v>
       </c>
     </row>
@@ -33425,7 +33423,7 @@
         <v>452</v>
       </c>
       <c r="D97" s="21">
-        <f>IFERROR(VLOOKUP(A97,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A97,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>395</v>
       </c>
     </row>
@@ -33441,7 +33439,7 @@
         <v>473</v>
       </c>
       <c r="D98" s="21">
-        <f>IFERROR(VLOOKUP(A98,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A98,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>565</v>
       </c>
     </row>
@@ -33457,7 +33455,7 @@
         <v>719</v>
       </c>
       <c r="D99" s="21">
-        <f>IFERROR(VLOOKUP(A99,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A99,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>756</v>
       </c>
     </row>
@@ -33473,7 +33471,7 @@
         <v>205</v>
       </c>
       <c r="D100" s="21">
-        <f>IFERROR(VLOOKUP(A100,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A100,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>302</v>
       </c>
     </row>
@@ -33489,7 +33487,7 @@
         <v>42</v>
       </c>
       <c r="D101" s="21">
-        <f>IFERROR(VLOOKUP(A101,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A101,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>90</v>
       </c>
     </row>
@@ -33505,7 +33503,7 @@
         <v>244</v>
       </c>
       <c r="D102" s="21">
-        <f>IFERROR(VLOOKUP(A102,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A102,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>532</v>
       </c>
     </row>
@@ -33521,7 +33519,7 @@
         <v>348</v>
       </c>
       <c r="D103" s="21">
-        <f>IFERROR(VLOOKUP(A103,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A103,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>352</v>
       </c>
     </row>
@@ -33537,7 +33535,7 @@
         <v>14</v>
       </c>
       <c r="D104" s="21">
-        <f>IFERROR(VLOOKUP(A104,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A104,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>53</v>
       </c>
     </row>
@@ -33553,7 +33551,7 @@
         <v>40</v>
       </c>
       <c r="D105" s="21">
-        <f>IFERROR(VLOOKUP(A105,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A105,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>50</v>
       </c>
     </row>
@@ -33569,7 +33567,7 @@
         <v>248</v>
       </c>
       <c r="D106" s="21">
-        <f>IFERROR(VLOOKUP(A106,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A106,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>294</v>
       </c>
     </row>
@@ -33585,7 +33583,7 @@
         <v>79</v>
       </c>
       <c r="D107" s="21">
-        <f>IFERROR(VLOOKUP(A107,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A107,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>70</v>
       </c>
     </row>
@@ -33601,7 +33599,7 @@
         <v>850</v>
       </c>
       <c r="D108" s="21">
-        <f>IFERROR(VLOOKUP(A108,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A108,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>659</v>
       </c>
     </row>
@@ -33617,7 +33615,7 @@
         <v>326</v>
       </c>
       <c r="D109" s="21">
-        <f>IFERROR(VLOOKUP(A109,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A109,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>283</v>
       </c>
     </row>
@@ -33633,7 +33631,7 @@
         <v>95</v>
       </c>
       <c r="D110" s="21">
-        <f>IFERROR(VLOOKUP(A110,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A110,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>89</v>
       </c>
     </row>
@@ -33649,7 +33647,7 @@
         <v>65</v>
       </c>
       <c r="D111" s="21">
-        <f>IFERROR(VLOOKUP(A111,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A111,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>324</v>
       </c>
     </row>
@@ -33665,7 +33663,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="21">
-        <f>IFERROR(VLOOKUP(A112,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A112,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>290</v>
       </c>
     </row>
@@ -33681,7 +33679,7 @@
         <v>92</v>
       </c>
       <c r="D113" s="21">
-        <f>IFERROR(VLOOKUP(A113,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A113,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>75</v>
       </c>
     </row>
@@ -33697,7 +33695,7 @@
         <v>273</v>
       </c>
       <c r="D114" s="21">
-        <f>IFERROR(VLOOKUP(A114,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A114,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>386</v>
       </c>
     </row>
@@ -33713,7 +33711,7 @@
         <v>29</v>
       </c>
       <c r="D115" s="21">
-        <f>IFERROR(VLOOKUP(A115,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A115,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>44</v>
       </c>
     </row>
@@ -33729,7 +33727,7 @@
         <v>1666</v>
       </c>
       <c r="D116" s="21">
-        <f>IFERROR(VLOOKUP(A116,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A116,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>2009</v>
       </c>
     </row>
@@ -33745,7 +33743,7 @@
         <v>154</v>
       </c>
       <c r="D117" s="21">
-        <f>IFERROR(VLOOKUP(A117,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A117,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>234</v>
       </c>
     </row>
@@ -33761,7 +33759,7 @@
         <v>9655</v>
       </c>
       <c r="D118" s="21">
-        <f>IFERROR(VLOOKUP(A118,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A118,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>14720</v>
       </c>
     </row>
@@ -33777,7 +33775,7 @@
         <v>274</v>
       </c>
       <c r="D119" s="21">
-        <f>IFERROR(VLOOKUP(A119,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A119,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>364</v>
       </c>
     </row>
@@ -33793,7 +33791,7 @@
         <v>45</v>
       </c>
       <c r="D120" s="21">
-        <f>IFERROR(VLOOKUP(A120,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A120,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>70</v>
       </c>
     </row>
@@ -33809,7 +33807,7 @@
         <v>83</v>
       </c>
       <c r="D121" s="21">
-        <f>IFERROR(VLOOKUP(A121,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A121,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>127</v>
       </c>
     </row>
@@ -33825,7 +33823,7 @@
         <v>279</v>
       </c>
       <c r="D122" s="21">
-        <f>IFERROR(VLOOKUP(A122,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A122,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>656</v>
       </c>
     </row>
@@ -33841,7 +33839,7 @@
         <v>232</v>
       </c>
       <c r="D123" s="21">
-        <f>IFERROR(VLOOKUP(A123,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A123,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>339</v>
       </c>
     </row>
@@ -33857,7 +33855,7 @@
         <v>154</v>
       </c>
       <c r="D124" s="21">
-        <f>IFERROR(VLOOKUP(A124,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A124,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>247</v>
       </c>
     </row>
@@ -33873,7 +33871,7 @@
         <v>298</v>
       </c>
       <c r="D125" s="21">
-        <f>IFERROR(VLOOKUP(A125,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A125,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>345</v>
       </c>
     </row>
@@ -33889,7 +33887,7 @@
         <v>185</v>
       </c>
       <c r="D126" s="21">
-        <f>IFERROR(VLOOKUP(A126,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A126,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>336</v>
       </c>
     </row>
@@ -33905,7 +33903,7 @@
         <v>803</v>
       </c>
       <c r="D127" s="21">
-        <f>IFERROR(VLOOKUP(A127,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A127,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>975</v>
       </c>
     </row>
@@ -33921,7 +33919,7 @@
         <v>176</v>
       </c>
       <c r="D128" s="21">
-        <f>IFERROR(VLOOKUP(A128,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A128,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>152</v>
       </c>
     </row>
@@ -33937,7 +33935,7 @@
         <v>706</v>
       </c>
       <c r="D129" s="21">
-        <f>IFERROR(VLOOKUP(A129,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A129,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>506</v>
       </c>
     </row>
@@ -33953,7 +33951,7 @@
         <v>226</v>
       </c>
       <c r="D130" s="21">
-        <f>IFERROR(VLOOKUP(A130,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A130,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>514</v>
       </c>
     </row>
@@ -33969,7 +33967,7 @@
         <v>144</v>
       </c>
       <c r="D131" s="21">
-        <f>IFERROR(VLOOKUP(A131,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A131,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>196</v>
       </c>
     </row>
@@ -33985,7 +33983,7 @@
         <v>199</v>
       </c>
       <c r="D132" s="21">
-        <f>IFERROR(VLOOKUP(A132,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A132,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>395</v>
       </c>
     </row>
@@ -34001,7 +33999,7 @@
         <v>297</v>
       </c>
       <c r="D133" s="21">
-        <f>IFERROR(VLOOKUP(A133,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A133,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>492</v>
       </c>
     </row>
@@ -34017,7 +34015,7 @@
         <v>360</v>
       </c>
       <c r="D134" s="21">
-        <f>IFERROR(VLOOKUP(A134,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A134,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>393</v>
       </c>
     </row>
@@ -34033,7 +34031,7 @@
         <v>60</v>
       </c>
       <c r="D135" s="21">
-        <f>IFERROR(VLOOKUP(A135,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A135,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>74</v>
       </c>
     </row>
@@ -34049,7 +34047,7 @@
         <v>717</v>
       </c>
       <c r="D136" s="21">
-        <f>IFERROR(VLOOKUP(A136,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A136,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>838</v>
       </c>
     </row>
@@ -34065,7 +34063,7 @@
         <v>211</v>
       </c>
       <c r="D137" s="21">
-        <f>IFERROR(VLOOKUP(A137,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A137,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>241</v>
       </c>
     </row>
@@ -34081,7 +34079,7 @@
         <v>240</v>
       </c>
       <c r="D138" s="21">
-        <f>IFERROR(VLOOKUP(A138,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A138,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>355</v>
       </c>
     </row>
@@ -34097,7 +34095,7 @@
         <v>1521</v>
       </c>
       <c r="D139" s="21">
-        <f>IFERROR(VLOOKUP(A139,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A139,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>2709</v>
       </c>
     </row>
@@ -34113,7 +34111,7 @@
         <v>627</v>
       </c>
       <c r="D140" s="21">
-        <f>IFERROR(VLOOKUP(A140,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A140,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1103</v>
       </c>
     </row>
@@ -34129,7 +34127,7 @@
         <v>613</v>
       </c>
       <c r="D141" s="21">
-        <f>IFERROR(VLOOKUP(A141,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A141,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>988</v>
       </c>
     </row>
@@ -34145,7 +34143,7 @@
         <v>861</v>
       </c>
       <c r="D142" s="21">
-        <f>IFERROR(VLOOKUP(A142,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A142,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1314</v>
       </c>
     </row>
@@ -34161,7 +34159,7 @@
         <v>466</v>
       </c>
       <c r="D143" s="21">
-        <f>IFERROR(VLOOKUP(A143,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A143,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1043</v>
       </c>
     </row>
@@ -34177,7 +34175,7 @@
         <v>2865</v>
       </c>
       <c r="D144" s="21">
-        <f>IFERROR(VLOOKUP(A144,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A144,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>4714</v>
       </c>
     </row>
@@ -34193,7 +34191,7 @@
         <v>459</v>
       </c>
       <c r="D145" s="21">
-        <f>IFERROR(VLOOKUP(A145,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A145,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>565</v>
       </c>
     </row>
@@ -34209,7 +34207,7 @@
         <v>1222</v>
       </c>
       <c r="D146" s="21">
-        <f>IFERROR(VLOOKUP(A146,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A146,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1559</v>
       </c>
     </row>
@@ -34225,7 +34223,7 @@
         <v>322</v>
       </c>
       <c r="D147" s="21">
-        <f>IFERROR(VLOOKUP(A147,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A147,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>675</v>
       </c>
     </row>
@@ -34241,7 +34239,7 @@
         <v>215</v>
       </c>
       <c r="D148" s="21">
-        <f>IFERROR(VLOOKUP(A148,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A148,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>235</v>
       </c>
     </row>
@@ -34257,7 +34255,7 @@
         <v>174</v>
       </c>
       <c r="D149" s="21">
-        <f>IFERROR(VLOOKUP(A149,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A149,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>186</v>
       </c>
     </row>
@@ -34273,7 +34271,7 @@
         <v>275</v>
       </c>
       <c r="D150" s="21">
-        <f>IFERROR(VLOOKUP(A150,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A150,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>307</v>
       </c>
     </row>
@@ -34289,7 +34287,7 @@
         <v>271</v>
       </c>
       <c r="D151" s="21">
-        <f>IFERROR(VLOOKUP(A151,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A151,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>364</v>
       </c>
     </row>
@@ -34305,7 +34303,7 @@
         <v>707</v>
       </c>
       <c r="D152" s="21">
-        <f>IFERROR(VLOOKUP(A152,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A152,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>934</v>
       </c>
     </row>
@@ -34321,7 +34319,7 @@
         <v>271</v>
       </c>
       <c r="D153" s="21">
-        <f>IFERROR(VLOOKUP(A153,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A153,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>663</v>
       </c>
     </row>
@@ -34337,7 +34335,7 @@
         <v>355</v>
       </c>
       <c r="D154" s="21">
-        <f>IFERROR(VLOOKUP(A154,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A154,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>374</v>
       </c>
     </row>
@@ -34353,7 +34351,7 @@
         <v>51</v>
       </c>
       <c r="D155" s="21">
-        <f>IFERROR(VLOOKUP(A155,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A155,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>87</v>
       </c>
     </row>
@@ -34369,7 +34367,7 @@
         <v>38</v>
       </c>
       <c r="D156" s="21">
-        <f>IFERROR(VLOOKUP(A156,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A156,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>70</v>
       </c>
     </row>
@@ -34385,7 +34383,7 @@
         <v/>
       </c>
       <c r="D157" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A157,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A157,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -34401,7 +34399,7 @@
         <v>777</v>
       </c>
       <c r="D158" s="21">
-        <f>IFERROR(VLOOKUP(A158,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A158,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>957</v>
       </c>
     </row>
@@ -34417,7 +34415,7 @@
         <v>597</v>
       </c>
       <c r="D159" s="21">
-        <f>IFERROR(VLOOKUP(A159,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A159,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>505</v>
       </c>
     </row>
@@ -34433,7 +34431,7 @@
         <v>491</v>
       </c>
       <c r="D160" s="21">
-        <f>IFERROR(VLOOKUP(A160,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A160,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>622</v>
       </c>
     </row>
@@ -34449,7 +34447,7 @@
         <v>57</v>
       </c>
       <c r="D161" s="21">
-        <f>IFERROR(VLOOKUP(A161,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A161,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>63</v>
       </c>
     </row>
@@ -34465,7 +34463,7 @@
         <v/>
       </c>
       <c r="D162" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A162,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A162,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -34481,7 +34479,7 @@
         <v>153</v>
       </c>
       <c r="D163" s="21">
-        <f>IFERROR(VLOOKUP(A163,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A163,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>256</v>
       </c>
     </row>
@@ -34497,7 +34495,7 @@
         <v>576</v>
       </c>
       <c r="D164" s="21">
-        <f>IFERROR(VLOOKUP(A164,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A164,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>704</v>
       </c>
     </row>
@@ -34513,7 +34511,7 @@
         <v>220</v>
       </c>
       <c r="D165" s="21">
-        <f>IFERROR(VLOOKUP(A165,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A165,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>244</v>
       </c>
     </row>
@@ -34529,7 +34527,7 @@
         <v>4670</v>
       </c>
       <c r="D166" s="21">
-        <f>IFERROR(VLOOKUP(A166,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A166,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>8178</v>
       </c>
     </row>
@@ -34545,7 +34543,7 @@
         <v>238</v>
       </c>
       <c r="D167" s="21">
-        <f>IFERROR(VLOOKUP(A167,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A167,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>792</v>
       </c>
     </row>
@@ -34561,7 +34559,7 @@
         <v>23</v>
       </c>
       <c r="D168" s="21">
-        <f>IFERROR(VLOOKUP(A168,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A168,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>119</v>
       </c>
     </row>
@@ -34577,7 +34575,7 @@
         <v>154</v>
       </c>
       <c r="D169" s="21">
-        <f>IFERROR(VLOOKUP(A169,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A169,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>125</v>
       </c>
     </row>
@@ -34593,7 +34591,7 @@
         <v>1174</v>
       </c>
       <c r="D170" s="21">
-        <f>IFERROR(VLOOKUP(A170,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A170,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1111</v>
       </c>
     </row>
@@ -34609,7 +34607,7 @@
         <v>12</v>
       </c>
       <c r="D171" s="21">
-        <f>IFERROR(VLOOKUP(A171,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A171,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>68</v>
       </c>
     </row>
@@ -34625,7 +34623,7 @@
         <v>325</v>
       </c>
       <c r="D172" s="21">
-        <f>IFERROR(VLOOKUP(A172,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A172,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>723</v>
       </c>
     </row>
@@ -34641,7 +34639,7 @@
         <v>67</v>
       </c>
       <c r="D173" s="21">
-        <f>IFERROR(VLOOKUP(A173,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A173,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>159</v>
       </c>
     </row>
@@ -34657,7 +34655,7 @@
         <v>76</v>
       </c>
       <c r="D174" s="21">
-        <f>IFERROR(VLOOKUP(A174,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A174,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>158</v>
       </c>
     </row>
@@ -34673,7 +34671,7 @@
         <v>129</v>
       </c>
       <c r="D175" s="21">
-        <f>IFERROR(VLOOKUP(A175,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A175,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>128</v>
       </c>
     </row>
@@ -34689,7 +34687,7 @@
         <v>124</v>
       </c>
       <c r="D176" s="21">
-        <f>IFERROR(VLOOKUP(A176,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A176,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>144</v>
       </c>
     </row>
@@ -34705,7 +34703,7 @@
         <v>14</v>
       </c>
       <c r="D177" s="21">
-        <f>IFERROR(VLOOKUP(A177,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A177,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>71</v>
       </c>
     </row>
@@ -34721,7 +34719,7 @@
         <v>16</v>
       </c>
       <c r="D178" s="21">
-        <f>IFERROR(VLOOKUP(A178,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A178,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>40</v>
       </c>
     </row>
@@ -34737,7 +34735,7 @@
         <v>1</v>
       </c>
       <c r="D179" s="21">
-        <f>IFERROR(VLOOKUP(A179,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A179,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>13</v>
       </c>
     </row>
@@ -34753,7 +34751,7 @@
         <v>25</v>
       </c>
       <c r="D180" s="21">
-        <f>IFERROR(VLOOKUP(A180,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A180,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>48</v>
       </c>
     </row>
@@ -34769,7 +34767,7 @@
         <v>45</v>
       </c>
       <c r="D181" s="21">
-        <f>IFERROR(VLOOKUP(A181,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A181,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>218</v>
       </c>
     </row>
@@ -34785,7 +34783,7 @@
         <v>67</v>
       </c>
       <c r="D182" s="21">
-        <f>IFERROR(VLOOKUP(A182,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A182,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -34801,7 +34799,7 @@
         <v>1</v>
       </c>
       <c r="D183" s="21">
-        <f>IFERROR(VLOOKUP(A183,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A183,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>87</v>
       </c>
     </row>
@@ -34817,7 +34815,7 @@
         <v>479</v>
       </c>
       <c r="D184" s="21">
-        <f>IFERROR(VLOOKUP(A184,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A184,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>492</v>
       </c>
     </row>
@@ -34833,7 +34831,7 @@
         <v>93</v>
       </c>
       <c r="D185" s="21">
-        <f>IFERROR(VLOOKUP(A185,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A185,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>161</v>
       </c>
     </row>
@@ -34849,7 +34847,7 @@
         <v>1174</v>
       </c>
       <c r="D186" s="21">
-        <f>IFERROR(VLOOKUP(A186,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A186,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>552</v>
       </c>
     </row>
@@ -34865,7 +34863,7 @@
         <v>60</v>
       </c>
       <c r="D187" s="21">
-        <f>IFERROR(VLOOKUP(A187,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A187,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>79</v>
       </c>
     </row>
@@ -34881,7 +34879,7 @@
         <v>175</v>
       </c>
       <c r="D188" s="21">
-        <f>IFERROR(VLOOKUP(A188,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A188,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>245</v>
       </c>
     </row>
@@ -34897,7 +34895,7 @@
         <v>19</v>
       </c>
       <c r="D189" s="21">
-        <f>IFERROR(VLOOKUP(A189,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A189,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>31</v>
       </c>
     </row>
@@ -34913,7 +34911,7 @@
         <v>61</v>
       </c>
       <c r="D190" s="21">
-        <f>IFERROR(VLOOKUP(A190,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A190,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>67</v>
       </c>
     </row>
@@ -34929,7 +34927,7 @@
         <v>79</v>
       </c>
       <c r="D191" s="21">
-        <f>IFERROR(VLOOKUP(A191,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A191,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>462</v>
       </c>
     </row>
@@ -34945,7 +34943,7 @@
         <v>0</v>
       </c>
       <c r="D192" s="21">
-        <f>IFERROR(VLOOKUP(A192,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A192,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>132</v>
       </c>
     </row>
@@ -34961,7 +34959,7 @@
         <v>285</v>
       </c>
       <c r="D193" s="21">
-        <f>IFERROR(VLOOKUP(A193,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A193,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>472</v>
       </c>
     </row>
@@ -34977,7 +34975,7 @@
         <v>117</v>
       </c>
       <c r="D194" s="21">
-        <f>IFERROR(VLOOKUP(A194,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A194,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -34993,7 +34991,7 @@
         <v>11</v>
       </c>
       <c r="D195" s="21">
-        <f>IFERROR(VLOOKUP(A195,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A195,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>145</v>
       </c>
     </row>
@@ -35009,7 +35007,7 @@
         <v>201</v>
       </c>
       <c r="D196" s="21">
-        <f>IFERROR(VLOOKUP(A196,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A196,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>280</v>
       </c>
     </row>
@@ -35025,7 +35023,7 @@
         <v>0</v>
       </c>
       <c r="D197" s="21">
-        <f>IFERROR(VLOOKUP(A197,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A197,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>29</v>
       </c>
     </row>
@@ -35041,7 +35039,7 @@
         <v>0</v>
       </c>
       <c r="D198" s="21">
-        <f>IFERROR(VLOOKUP(A198,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A198,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>33</v>
       </c>
     </row>
@@ -35057,7 +35055,7 @@
         <v>0</v>
       </c>
       <c r="D199" s="21">
-        <f>IFERROR(VLOOKUP(A199,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A199,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>158</v>
       </c>
     </row>
@@ -35073,7 +35071,7 @@
         <v>40</v>
       </c>
       <c r="D200" s="21">
-        <f>IFERROR(VLOOKUP(A200,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A200,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>354</v>
       </c>
     </row>
@@ -35089,7 +35087,7 @@
         <v>1630</v>
       </c>
       <c r="D201" s="21">
-        <f>IFERROR(VLOOKUP(A201,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A201,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3657</v>
       </c>
     </row>
@@ -35105,7 +35103,7 @@
         <v>745</v>
       </c>
       <c r="D202" s="21">
-        <f>IFERROR(VLOOKUP(A202,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A202,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1267</v>
       </c>
     </row>
@@ -35121,7 +35119,7 @@
         <v>314</v>
       </c>
       <c r="D203" s="21">
-        <f>IFERROR(VLOOKUP(A203,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A203,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>500</v>
       </c>
     </row>
@@ -35137,7 +35135,7 @@
         <v>98</v>
       </c>
       <c r="D204" s="21">
-        <f>IFERROR(VLOOKUP(A204,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A204,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>128</v>
       </c>
     </row>
@@ -35153,7 +35151,7 @@
         <v>0</v>
       </c>
       <c r="D205" s="21">
-        <f>IFERROR(VLOOKUP(A205,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A205,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -35169,7 +35167,7 @@
         <v>331</v>
       </c>
       <c r="D206" s="21">
-        <f>IFERROR(VLOOKUP(A206,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A206,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>439</v>
       </c>
     </row>
@@ -35185,7 +35183,7 @@
         <v>270</v>
       </c>
       <c r="D207" s="21">
-        <f>IFERROR(VLOOKUP(A207,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A207,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>505</v>
       </c>
     </row>
@@ -35201,7 +35199,7 @@
         <v/>
       </c>
       <c r="D208" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A208,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A208,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -35217,7 +35215,7 @@
         <v>846</v>
       </c>
       <c r="D209" s="21">
-        <f>IFERROR(VLOOKUP(A209,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A209,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1302</v>
       </c>
     </row>
@@ -35233,7 +35231,7 @@
         <v>270</v>
       </c>
       <c r="D210" s="21">
-        <f>IFERROR(VLOOKUP(A210,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A210,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>643</v>
       </c>
     </row>
@@ -35249,7 +35247,7 @@
         <v>20</v>
       </c>
       <c r="D211" s="21">
-        <f>IFERROR(VLOOKUP(A211,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A211,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>54</v>
       </c>
     </row>
@@ -35265,7 +35263,7 @@
         <v>537</v>
       </c>
       <c r="D212" s="21">
-        <f>IFERROR(VLOOKUP(A212,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A212,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>503</v>
       </c>
     </row>
@@ -35281,7 +35279,7 @@
         <v>359</v>
       </c>
       <c r="D213" s="21">
-        <f>IFERROR(VLOOKUP(A213,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A213,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>296</v>
       </c>
     </row>
@@ -35297,7 +35295,7 @@
         <v>786</v>
       </c>
       <c r="D214" s="21">
-        <f>IFERROR(VLOOKUP(A214,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A214,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1064</v>
       </c>
     </row>
@@ -35313,7 +35311,7 @@
         <v>296</v>
       </c>
       <c r="D215" s="21">
-        <f>IFERROR(VLOOKUP(A215,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A215,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>210</v>
       </c>
     </row>
@@ -35329,7 +35327,7 @@
         <v/>
       </c>
       <c r="D216" s="21">
-        <f>IFERROR(VLOOKUP(A216,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A216,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>795</v>
       </c>
     </row>
@@ -35345,7 +35343,7 @@
         <v>306</v>
       </c>
       <c r="D217" s="21">
-        <f>IFERROR(VLOOKUP(A217,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A217,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>411</v>
       </c>
     </row>
@@ -35361,7 +35359,7 @@
         <v>426</v>
       </c>
       <c r="D218" s="21">
-        <f>IFERROR(VLOOKUP(A218,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A218,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>415</v>
       </c>
     </row>
@@ -35377,7 +35375,7 @@
         <v>1005</v>
       </c>
       <c r="D219" s="21">
-        <f>IFERROR(VLOOKUP(A219,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A219,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>833</v>
       </c>
     </row>
@@ -35393,7 +35391,7 @@
         <v>457</v>
       </c>
       <c r="D220" s="21">
-        <f>IFERROR(VLOOKUP(A220,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A220,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>78</v>
       </c>
     </row>
@@ -35409,7 +35407,7 @@
         <v>448</v>
       </c>
       <c r="D221" s="21">
-        <f>IFERROR(VLOOKUP(A221,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A221,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>515</v>
       </c>
     </row>
@@ -35425,7 +35423,7 @@
         <v>131</v>
       </c>
       <c r="D222" s="21">
-        <f>IFERROR(VLOOKUP(A222,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A222,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>313</v>
       </c>
     </row>
@@ -35441,7 +35439,7 @@
         <v>1451</v>
       </c>
       <c r="D223" s="21">
-        <f>IFERROR(VLOOKUP(A223,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A223,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1128</v>
       </c>
     </row>
@@ -35457,7 +35455,7 @@
         <v>152</v>
       </c>
       <c r="D224" s="21">
-        <f>IFERROR(VLOOKUP(A224,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A224,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>138</v>
       </c>
     </row>
@@ -35473,7 +35471,7 @@
         <v>265</v>
       </c>
       <c r="D225" s="21">
-        <f>IFERROR(VLOOKUP(A225,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A225,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>501</v>
       </c>
     </row>
@@ -35489,7 +35487,7 @@
         <v>117</v>
       </c>
       <c r="D226" s="21">
-        <f>IFERROR(VLOOKUP(A226,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A226,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>48</v>
       </c>
     </row>
@@ -35505,7 +35503,7 @@
         <v>90</v>
       </c>
       <c r="D227" s="21">
-        <f>IFERROR(VLOOKUP(A227,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A227,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>84</v>
       </c>
     </row>
@@ -35521,7 +35519,7 @@
         <v/>
       </c>
       <c r="D228" s="21">
-        <f>IFERROR(VLOOKUP(A228,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A228,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>5</v>
       </c>
     </row>
@@ -35537,7 +35535,7 @@
         <v>14</v>
       </c>
       <c r="D229" s="21">
-        <f>IFERROR(VLOOKUP(A229,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A229,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>53</v>
       </c>
     </row>
@@ -35553,7 +35551,7 @@
         <v>499</v>
       </c>
       <c r="D230" s="21">
-        <f>IFERROR(VLOOKUP(A230,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A230,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1313</v>
       </c>
     </row>
@@ -35569,7 +35567,7 @@
         <v>388</v>
       </c>
       <c r="D231" s="21">
-        <f>IFERROR(VLOOKUP(A231,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A231,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>565</v>
       </c>
     </row>
@@ -35585,7 +35583,7 @@
         <v>266</v>
       </c>
       <c r="D232" s="21">
-        <f>IFERROR(VLOOKUP(A232,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A232,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>364</v>
       </c>
     </row>
@@ -35601,7 +35599,7 @@
         <v>658</v>
       </c>
       <c r="D233" s="21">
-        <f>IFERROR(VLOOKUP(A233,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A233,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1146</v>
       </c>
     </row>
@@ -35617,7 +35615,7 @@
         <v>284</v>
       </c>
       <c r="D234" s="21">
-        <f>IFERROR(VLOOKUP(A234,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A234,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>629</v>
       </c>
     </row>
@@ -35633,7 +35631,7 @@
         <v>90</v>
       </c>
       <c r="D235" s="21">
-        <f>IFERROR(VLOOKUP(A235,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A235,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>405</v>
       </c>
     </row>
@@ -35649,7 +35647,7 @@
         <v/>
       </c>
       <c r="D236" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A236,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A236,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -35665,7 +35663,7 @@
         <v>133</v>
       </c>
       <c r="D237" s="21">
-        <f>IFERROR(VLOOKUP(A237,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A237,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>72</v>
       </c>
     </row>
@@ -35681,7 +35679,7 @@
         <v>209</v>
       </c>
       <c r="D238" s="21">
-        <f>IFERROR(VLOOKUP(A238,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A238,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>203</v>
       </c>
     </row>
@@ -35697,7 +35695,7 @@
         <v>305</v>
       </c>
       <c r="D239" s="21">
-        <f>IFERROR(VLOOKUP(A239,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A239,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>451</v>
       </c>
     </row>
@@ -35713,7 +35711,7 @@
         <v>173</v>
       </c>
       <c r="D240" s="21">
-        <f>IFERROR(VLOOKUP(A240,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A240,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>170</v>
       </c>
     </row>
@@ -35729,7 +35727,7 @@
         <v>392</v>
       </c>
       <c r="D241" s="21">
-        <f>IFERROR(VLOOKUP(A241,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A241,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>745</v>
       </c>
     </row>
@@ -35745,7 +35743,7 @@
         <v>28</v>
       </c>
       <c r="D242" s="21">
-        <f>IFERROR(VLOOKUP(A242,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A242,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>94</v>
       </c>
     </row>
@@ -35761,7 +35759,7 @@
         <v>2196</v>
       </c>
       <c r="D243" s="21">
-        <f>IFERROR(VLOOKUP(A243,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A243,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3802</v>
       </c>
     </row>
@@ -35777,7 +35775,7 @@
         <v>499</v>
       </c>
       <c r="D244" s="21">
-        <f>IFERROR(VLOOKUP(A244,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A244,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>990</v>
       </c>
     </row>
@@ -35793,7 +35791,7 @@
         <v>286</v>
       </c>
       <c r="D245" s="21">
-        <f>IFERROR(VLOOKUP(A245,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A245,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>424</v>
       </c>
     </row>
@@ -35809,7 +35807,7 @@
         <v>582</v>
       </c>
       <c r="D246" s="21">
-        <f>IFERROR(VLOOKUP(A246,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A246,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1144</v>
       </c>
     </row>
@@ -35825,7 +35823,7 @@
         <v>216</v>
       </c>
       <c r="D247" s="21">
-        <f>IFERROR(VLOOKUP(A247,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A247,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>418</v>
       </c>
     </row>
@@ -35841,7 +35839,7 @@
         <v>419</v>
       </c>
       <c r="D248" s="21">
-        <f>IFERROR(VLOOKUP(A248,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A248,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>718</v>
       </c>
     </row>
@@ -35857,7 +35855,7 @@
         <v>293</v>
       </c>
       <c r="D249" s="21">
-        <f>IFERROR(VLOOKUP(A249,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A249,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>517</v>
       </c>
     </row>
@@ -35873,7 +35871,7 @@
         <v>51</v>
       </c>
       <c r="D250" s="21">
-        <f>IFERROR(VLOOKUP(A250,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A250,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>396</v>
       </c>
     </row>
@@ -35889,7 +35887,7 @@
         <v>741</v>
       </c>
       <c r="D251" s="21">
-        <f>IFERROR(VLOOKUP(A251,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A251,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>951</v>
       </c>
     </row>
@@ -35905,7 +35903,7 @@
         <v>218</v>
       </c>
       <c r="D252" s="21">
-        <f>IFERROR(VLOOKUP(A252,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A252,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>555</v>
       </c>
     </row>
@@ -35921,7 +35919,7 @@
         <v>385</v>
       </c>
       <c r="D253" s="21">
-        <f>IFERROR(VLOOKUP(A253,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A253,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>657</v>
       </c>
     </row>
@@ -35937,7 +35935,7 @@
         <v>11653</v>
       </c>
       <c r="D254" s="21">
-        <f>IFERROR(VLOOKUP(A254,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A254,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>24601</v>
       </c>
     </row>
@@ -35953,7 +35951,7 @@
         <v>913</v>
       </c>
       <c r="D255" s="21">
-        <f>IFERROR(VLOOKUP(A255,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A255,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3009</v>
       </c>
     </row>
@@ -35969,7 +35967,7 @@
         <v>283</v>
       </c>
       <c r="D256" s="21">
-        <f>IFERROR(VLOOKUP(A256,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A256,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>768</v>
       </c>
     </row>
@@ -35985,7 +35983,7 @@
         <v>1003</v>
       </c>
       <c r="D257" s="21">
-        <f>IFERROR(VLOOKUP(A257,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A257,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>2584</v>
       </c>
     </row>
@@ -36001,7 +35999,7 @@
         <v>434</v>
       </c>
       <c r="D258" s="21">
-        <f>IFERROR(VLOOKUP(A258,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A258,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1116</v>
       </c>
     </row>
@@ -36017,7 +36015,7 @@
         <v>1481</v>
       </c>
       <c r="D259" s="21">
-        <f>IFERROR(VLOOKUP(A259,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A259,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>4534</v>
       </c>
     </row>
@@ -36033,7 +36031,7 @@
         <v>88</v>
       </c>
       <c r="D260" s="21">
-        <f>IFERROR(VLOOKUP(A260,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A260,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>250</v>
       </c>
     </row>
@@ -36049,7 +36047,7 @@
         <v>233</v>
       </c>
       <c r="D261" s="21">
-        <f>IFERROR(VLOOKUP(A261,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A261,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>13</v>
       </c>
     </row>
@@ -36065,7 +36063,7 @@
         <v>78</v>
       </c>
       <c r="D262" s="21">
-        <f>IFERROR(VLOOKUP(A262,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A262,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3</v>
       </c>
     </row>
@@ -36081,7 +36079,7 @@
         <v>35</v>
       </c>
       <c r="D263" s="21">
-        <f>IFERROR(VLOOKUP(A263,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A263,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>2</v>
       </c>
     </row>
@@ -36097,7 +36095,7 @@
         <v>185</v>
       </c>
       <c r="D264" s="21">
-        <f>IFERROR(VLOOKUP(A264,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A264,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>429</v>
       </c>
     </row>
@@ -36113,7 +36111,7 @@
         <v>186</v>
       </c>
       <c r="D265" s="21">
-        <f>IFERROR(VLOOKUP(A265,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A265,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>427</v>
       </c>
     </row>
@@ -36129,7 +36127,7 @@
         <v>416</v>
       </c>
       <c r="D266" s="21">
-        <f>IFERROR(VLOOKUP(A266,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A266,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1230</v>
       </c>
     </row>
@@ -36145,7 +36143,7 @@
         <v>61</v>
       </c>
       <c r="D267" s="21">
-        <f>IFERROR(VLOOKUP(A267,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A267,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>191</v>
       </c>
     </row>
@@ -36161,7 +36159,7 @@
         <v>123</v>
       </c>
       <c r="D268" s="21">
-        <f>IFERROR(VLOOKUP(A268,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A268,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>36</v>
       </c>
     </row>
@@ -36177,7 +36175,7 @@
         <v>264</v>
       </c>
       <c r="D269" s="21">
-        <f>IFERROR(VLOOKUP(A269,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A269,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>588</v>
       </c>
     </row>
@@ -36193,7 +36191,7 @@
         <v>153</v>
       </c>
       <c r="D270" s="21">
-        <f>IFERROR(VLOOKUP(A270,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A270,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>37</v>
       </c>
     </row>
@@ -36209,7 +36207,7 @@
         <v>100</v>
       </c>
       <c r="D271" s="21">
-        <f>IFERROR(VLOOKUP(A271,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A271,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>297</v>
       </c>
     </row>
@@ -36225,7 +36223,7 @@
         <v>190</v>
       </c>
       <c r="D272" s="21">
-        <f>IFERROR(VLOOKUP(A272,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A272,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>419</v>
       </c>
     </row>
@@ -36241,7 +36239,7 @@
         <v>46</v>
       </c>
       <c r="D273" s="21">
-        <f>IFERROR(VLOOKUP(A273,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A273,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>145</v>
       </c>
     </row>
@@ -36257,7 +36255,7 @@
         <v>25</v>
       </c>
       <c r="D274" s="21">
-        <f>IFERROR(VLOOKUP(A274,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A274,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>22</v>
       </c>
     </row>
@@ -36273,7 +36271,7 @@
         <v>120</v>
       </c>
       <c r="D275" s="21">
-        <f>IFERROR(VLOOKUP(A275,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A275,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>140</v>
       </c>
     </row>
@@ -36289,7 +36287,7 @@
         <v>221</v>
       </c>
       <c r="D276" s="21">
-        <f>IFERROR(VLOOKUP(A276,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A276,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>596</v>
       </c>
     </row>
@@ -36305,7 +36303,7 @@
         <v>34</v>
       </c>
       <c r="D277" s="21">
-        <f>IFERROR(VLOOKUP(A277,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A277,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>21</v>
       </c>
     </row>
@@ -36321,7 +36319,7 @@
         <v>49</v>
       </c>
       <c r="D278" s="21">
-        <f>IFERROR(VLOOKUP(A278,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A278,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>39</v>
       </c>
     </row>
@@ -36337,7 +36335,7 @@
         <v>215</v>
       </c>
       <c r="D279" s="21">
-        <f>IFERROR(VLOOKUP(A279,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A279,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>115</v>
       </c>
     </row>
@@ -36353,7 +36351,7 @@
         <v>30</v>
       </c>
       <c r="D280" s="21">
-        <f>IFERROR(VLOOKUP(A280,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A280,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>25</v>
       </c>
     </row>
@@ -36369,7 +36367,7 @@
         <v>302</v>
       </c>
       <c r="D281" s="21">
-        <f>IFERROR(VLOOKUP(A281,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A281,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>39</v>
       </c>
     </row>
@@ -36385,7 +36383,7 @@
         <v>31</v>
       </c>
       <c r="D282" s="21">
-        <f>IFERROR(VLOOKUP(A282,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A282,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>10</v>
       </c>
     </row>
@@ -36401,7 +36399,7 @@
         <v>38</v>
       </c>
       <c r="D283" s="21">
-        <f>IFERROR(VLOOKUP(A283,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A283,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3</v>
       </c>
     </row>
@@ -36417,7 +36415,7 @@
         <v>42</v>
       </c>
       <c r="D284" s="21">
-        <f>IFERROR(VLOOKUP(A284,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A284,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>7</v>
       </c>
     </row>
@@ -36433,7 +36431,7 @@
         <v/>
       </c>
       <c r="D285" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A285,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A285,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -36449,7 +36447,7 @@
         <v>198</v>
       </c>
       <c r="D286" s="21">
-        <f>IFERROR(VLOOKUP(A286,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A286,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>61</v>
       </c>
     </row>
@@ -36465,7 +36463,7 @@
         <v>157</v>
       </c>
       <c r="D287" s="21">
-        <f>IFERROR(VLOOKUP(A287,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A287,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>19</v>
       </c>
     </row>
@@ -36481,7 +36479,7 @@
         <v>134</v>
       </c>
       <c r="D288" s="21">
-        <f>IFERROR(VLOOKUP(A288,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A288,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>28</v>
       </c>
     </row>
@@ -36497,7 +36495,7 @@
         <v>43</v>
       </c>
       <c r="D289" s="21">
-        <f>IFERROR(VLOOKUP(A289,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A289,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3</v>
       </c>
     </row>
@@ -36513,7 +36511,7 @@
         <v>756</v>
       </c>
       <c r="D290" s="21">
-        <f>IFERROR(VLOOKUP(A290,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A290,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>1838</v>
       </c>
     </row>
@@ -36529,7 +36527,7 @@
         <v>153</v>
       </c>
       <c r="D291" s="21">
-        <f>IFERROR(VLOOKUP(A291,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A291,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>335</v>
       </c>
     </row>
@@ -36545,7 +36543,7 @@
         <v>158</v>
       </c>
       <c r="D292" s="21">
-        <f>IFERROR(VLOOKUP(A292,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A292,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>402</v>
       </c>
     </row>
@@ -36561,7 +36559,7 @@
         <v>123</v>
       </c>
       <c r="D293" s="21">
-        <f>IFERROR(VLOOKUP(A293,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A293,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>243</v>
       </c>
     </row>
@@ -36577,7 +36575,7 @@
         <v>145</v>
       </c>
       <c r="D294" s="21">
-        <f>IFERROR(VLOOKUP(A294,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A294,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>324</v>
       </c>
     </row>
@@ -36593,7 +36591,7 @@
         <v>163</v>
       </c>
       <c r="D295" s="21">
-        <f>IFERROR(VLOOKUP(A295,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A295,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>67</v>
       </c>
     </row>
@@ -36609,7 +36607,7 @@
         <v>58</v>
       </c>
       <c r="D296" s="21">
-        <f>IFERROR(VLOOKUP(A296,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A296,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>25</v>
       </c>
     </row>
@@ -36625,7 +36623,7 @@
         <v>46</v>
       </c>
       <c r="D297" s="21">
-        <f>IFERROR(VLOOKUP(A297,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A297,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>19</v>
       </c>
     </row>
@@ -36641,7 +36639,7 @@
         <v>377</v>
       </c>
       <c r="D298" s="21">
-        <f>IFERROR(VLOOKUP(A298,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A298,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>134</v>
       </c>
     </row>
@@ -36657,7 +36655,7 @@
         <v>27</v>
       </c>
       <c r="D299" s="21">
-        <f>IFERROR(VLOOKUP(A299,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A299,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>14</v>
       </c>
     </row>
@@ -36673,7 +36671,7 @@
         <v>202</v>
       </c>
       <c r="D300" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A300,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A300,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -36689,7 +36687,7 @@
         <v>0</v>
       </c>
       <c r="D301" s="21">
-        <f>IFERROR(VLOOKUP(A301,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A301,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -36705,7 +36703,7 @@
         <v>189</v>
       </c>
       <c r="D302" s="21">
-        <f>IFERROR(VLOOKUP(A302,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A302,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>52</v>
       </c>
     </row>
@@ -36721,7 +36719,7 @@
         <v>115</v>
       </c>
       <c r="D303" s="21">
-        <f>IFERROR(VLOOKUP(A303,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A303,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>11</v>
       </c>
     </row>
@@ -36737,7 +36735,7 @@
         <v>299</v>
       </c>
       <c r="D304" s="21">
-        <f>IFERROR(VLOOKUP(A304,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A304,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>25</v>
       </c>
     </row>
@@ -36753,7 +36751,7 @@
         <v>214</v>
       </c>
       <c r="D305" s="21">
-        <f>IFERROR(VLOOKUP(A305,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A305,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>27</v>
       </c>
     </row>
@@ -36769,7 +36767,7 @@
         <v>33</v>
       </c>
       <c r="D306" s="21">
-        <f>IFERROR(VLOOKUP(A306,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A306,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>3</v>
       </c>
     </row>
@@ -36785,7 +36783,7 @@
         <v>182</v>
       </c>
       <c r="D307" s="21">
-        <f>IFERROR(VLOOKUP(A307,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A307,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>81</v>
       </c>
     </row>
@@ -36801,7 +36799,7 @@
         <v>46</v>
       </c>
       <c r="D308" s="21">
-        <f>IFERROR(VLOOKUP(A308,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A308,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>16</v>
       </c>
     </row>
@@ -36817,7 +36815,7 @@
         <v>53</v>
       </c>
       <c r="D309" s="21">
-        <f>IFERROR(VLOOKUP(A309,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A309,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>23</v>
       </c>
     </row>
@@ -36833,7 +36831,7 @@
         <v>458</v>
       </c>
       <c r="D310" s="21">
-        <f>IFERROR(VLOOKUP(A310,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A310,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>405</v>
       </c>
     </row>
@@ -36849,7 +36847,7 @@
         <v>6</v>
       </c>
       <c r="D311" s="21">
-        <f>IFERROR(VLOOKUP(A311,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A311,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>18</v>
       </c>
     </row>
@@ -36865,7 +36863,7 @@
         <v>0</v>
       </c>
       <c r="D312" s="21">
-        <f>IFERROR(VLOOKUP(A312,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A312,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>387</v>
       </c>
     </row>
@@ -36881,7 +36879,7 @@
         <v>0</v>
       </c>
       <c r="D313" s="21">
-        <f>IFERROR(VLOOKUP(A313,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A313,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>71</v>
       </c>
     </row>
@@ -36897,7 +36895,7 @@
         <v>25</v>
       </c>
       <c r="D314" s="21">
-        <f>IFERROR(VLOOKUP(A314,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A314,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>68</v>
       </c>
     </row>
@@ -36913,7 +36911,7 @@
         <v>202</v>
       </c>
       <c r="D315" s="21">
-        <f>IFERROR(VLOOKUP(A315,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A315,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>274</v>
       </c>
     </row>
@@ -36929,7 +36927,7 @@
         <v>3</v>
       </c>
       <c r="D316" s="21">
-        <f>IFERROR(VLOOKUP(A316,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A316,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>58</v>
       </c>
     </row>
@@ -36945,7 +36943,7 @@
         <v>75</v>
       </c>
       <c r="D317" s="21">
-        <f>IFERROR(VLOOKUP(A317,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A317,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>316</v>
       </c>
     </row>
@@ -36961,7 +36959,7 @@
         <v>5</v>
       </c>
       <c r="D318" s="21">
-        <f>IFERROR(VLOOKUP(A318,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A318,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>72</v>
       </c>
     </row>
@@ -36977,7 +36975,7 @@
         <v/>
       </c>
       <c r="D319" s="21">
-        <f>IFERROR(VLOOKUP(A319,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A319,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -36993,7 +36991,7 @@
         <v>39</v>
       </c>
       <c r="D320" s="21">
-        <f>IFERROR(VLOOKUP(A320,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A320,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>99</v>
       </c>
     </row>
@@ -37009,7 +37007,7 @@
         <v>4</v>
       </c>
       <c r="D321" s="21">
-        <f>IFERROR(VLOOKUP(A321,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A321,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>13</v>
       </c>
     </row>
@@ -37025,7 +37023,7 @@
         <v>48</v>
       </c>
       <c r="D322" s="21">
-        <f>IFERROR(VLOOKUP(A322,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A322,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>75</v>
       </c>
     </row>
@@ -37041,7 +37039,7 @@
         <v>15</v>
       </c>
       <c r="D323" s="21">
-        <f>IFERROR(VLOOKUP(A323,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A323,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>15</v>
       </c>
     </row>
@@ -37057,7 +37055,7 @@
         <v>31</v>
       </c>
       <c r="D324" s="21">
-        <f>IFERROR(VLOOKUP(A324,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A324,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>23</v>
       </c>
     </row>
@@ -37073,7 +37071,7 @@
         <v/>
       </c>
       <c r="D325" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A325,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A325,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37089,7 +37087,7 @@
         <v>10</v>
       </c>
       <c r="D326" s="21">
-        <f>IFERROR(VLOOKUP(A326,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A326,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>39</v>
       </c>
     </row>
@@ -37105,7 +37103,7 @@
         <v>0</v>
       </c>
       <c r="D327" s="21">
-        <f>IFERROR(VLOOKUP(A327,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A327,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>16</v>
       </c>
     </row>
@@ -37121,7 +37119,7 @@
         <v>0</v>
       </c>
       <c r="D328" s="21">
-        <f>IFERROR(VLOOKUP(A328,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A328,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>8</v>
       </c>
     </row>
@@ -37137,7 +37135,7 @@
         <v/>
       </c>
       <c r="D329" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A329,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A329,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37153,7 +37151,7 @@
         <v>238</v>
       </c>
       <c r="D330" s="21">
-        <f>IFERROR(VLOOKUP(A330,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A330,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>262</v>
       </c>
     </row>
@@ -37169,7 +37167,7 @@
         <v>32</v>
       </c>
       <c r="D331" s="21">
-        <f>IFERROR(VLOOKUP(A331,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A331,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>42</v>
       </c>
     </row>
@@ -37185,7 +37183,7 @@
         <v/>
       </c>
       <c r="D332" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A332,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A332,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37201,7 +37199,7 @@
         <v>1</v>
       </c>
       <c r="D333" s="21">
-        <f>IFERROR(VLOOKUP(A333,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A333,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>16</v>
       </c>
     </row>
@@ -37217,7 +37215,7 @@
         <v>32</v>
       </c>
       <c r="D334" s="21">
-        <f>IFERROR(VLOOKUP(A334,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A334,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>38</v>
       </c>
     </row>
@@ -37233,7 +37231,7 @@
         <v>3</v>
       </c>
       <c r="D335" s="21">
-        <f>IFERROR(VLOOKUP(A335,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A335,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v>4</v>
       </c>
     </row>
@@ -37248,9 +37246,9 @@
         <f>IFERROR(VLOOKUP(A336,datos_2016!$B$1:$G$330,4,FALSE),"")</f>
         <v>16</v>
       </c>
-      <c r="D336" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A336,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
-        <v/>
+      <c r="D336" s="21">
+        <f>IFERROR(VLOOKUP(A336,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
+        <v>42</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -37265,7 +37263,7 @@
         <v>0</v>
       </c>
       <c r="D337" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A337,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A337,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37280,9 +37278,9 @@
         <f>IFERROR(VLOOKUP(A338,datos_2016!$B$1:$G$330,4,FALSE),"")</f>
         <v>1</v>
       </c>
-      <c r="D338" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A338,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
-        <v/>
+      <c r="D338" s="21">
+        <f>IFERROR(VLOOKUP(A338,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
+        <v>11</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -37296,9 +37294,9 @@
         <f>IFERROR(VLOOKUP(A339,datos_2016!$B$1:$G$330,4,FALSE),"")</f>
         <v>2</v>
       </c>
-      <c r="D339" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A339,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
-        <v/>
+      <c r="D339" s="21">
+        <f>IFERROR(VLOOKUP(A339,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -37312,9 +37310,9 @@
         <f>IFERROR(VLOOKUP(A340,datos_2016!$B$1:$G$330,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D340" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A340,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
-        <v/>
+      <c r="D340" s="21">
+        <f>IFERROR(VLOOKUP(A340,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
+        <v>34</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -37329,7 +37327,7 @@
         <v/>
       </c>
       <c r="D341" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A341,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A341,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37345,7 +37343,7 @@
         <v>0</v>
       </c>
       <c r="D342" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A342,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A342,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37361,7 +37359,7 @@
         <v>0</v>
       </c>
       <c r="D343" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A343,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A343,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37377,7 +37375,7 @@
         <v/>
       </c>
       <c r="D344" s="21" t="str">
-        <f>IFERROR(VLOOKUP(A344,datos_2024!$B$1:$G$322,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(A344,datos_2024!$B$1:$G$326,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -37601,7 +37599,7 @@
       <c r="C2">
         <v>6852</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2">
         <v>14070</v>
       </c>
     </row>
@@ -37615,7 +37613,7 @@
       <c r="C3">
         <v>67975</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3">
         <v>85646</v>
       </c>
     </row>
@@ -37629,7 +37627,7 @@
       <c r="C4">
         <v>29528</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4">
         <v>43576</v>
       </c>
     </row>
@@ -37643,7 +37641,7 @@
       <c r="C5">
         <v>9955</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5">
         <v>15874</v>
       </c>
     </row>
@@ -37657,7 +37655,7 @@
       <c r="C6">
         <v>14789</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6">
         <v>22042</v>
       </c>
     </row>
@@ -37671,7 +37669,7 @@
       <c r="C7">
         <v>5886</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7">
         <v>10572</v>
       </c>
     </row>
@@ -37685,7 +37683,7 @@
       <c r="C8">
         <v>22903</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8">
         <v>45446</v>
       </c>
     </row>
@@ -37699,7 +37697,7 @@
       <c r="C9">
         <v>921</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9">
         <v>1957</v>
       </c>
     </row>
@@ -37713,7 +37711,7 @@
       <c r="C10">
         <v>325</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10">
         <v>471</v>
       </c>
     </row>
@@ -37727,7 +37725,7 @@
       <c r="C11" s="22">
         <v>1217</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="22">
         <v>2280</v>
       </c>
     </row>
@@ -37741,7 +37739,7 @@
       <c r="C12" s="22">
         <v>159134</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="22">
         <v>239654</v>
       </c>
     </row>
